--- a/Base.xlsx
+++ b/Base.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LK\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LK\Desktop\GItHubUpload\EVALUATION-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DEE9E7A-9935-4104-910E-49B40DA1336E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D8DC1A-8C4E-4DE2-8C1D-34498E0EEC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="Classification" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Classification!$A$1:$C$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Classification!$A$1:$C$306</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="788">
   <si>
     <t>Classe</t>
   </si>
@@ -2162,9 +2162,6 @@
     <t>Gestion des risques en finance</t>
   </si>
   <si>
-    <t>KAPNANG Brice Herman</t>
-  </si>
-  <si>
     <t>Modèles de courbes de taux</t>
   </si>
   <si>
@@ -2382,6 +2379,15 @@
   </si>
   <si>
     <t>Sport</t>
+  </si>
+  <si>
+    <t>AGBEDJINOU Léonard</t>
+  </si>
+  <si>
+    <t>NOUMEDEM Boris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCHUENTE </t>
   </si>
 </sst>
 </file>
@@ -9089,7 +9095,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A89" s="53" t="s">
         <v>108</v>
       </c>
@@ -9144,7 +9150,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="32.25" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A94" s="61" t="s">
         <v>108</v>
       </c>
@@ -9210,7 +9216,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="32.25" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A100" s="61" t="s">
         <v>138</v>
       </c>
@@ -10516,7 +10522,7 @@
         <v>711</v>
       </c>
       <c r="C218" t="s">
-        <v>712</v>
+        <v>786</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -10524,7 +10530,7 @@
         <v>338</v>
       </c>
       <c r="B219" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C219" t="s">
         <v>704</v>
@@ -10535,10 +10541,10 @@
         <v>338</v>
       </c>
       <c r="B220" t="s">
+        <v>713</v>
+      </c>
+      <c r="C220" t="s">
         <v>714</v>
-      </c>
-      <c r="C220" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -10546,7 +10552,7 @@
         <v>338</v>
       </c>
       <c r="B221" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C221" t="s">
         <v>513</v>
@@ -10557,10 +10563,10 @@
         <v>338</v>
       </c>
       <c r="B222" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C222" t="s">
-        <v>515</v>
+        <v>787</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -10568,10 +10574,10 @@
         <v>338</v>
       </c>
       <c r="B223" t="s">
+        <v>717</v>
+      </c>
+      <c r="C223" t="s">
         <v>718</v>
-      </c>
-      <c r="C223" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -10579,10 +10585,10 @@
         <v>338</v>
       </c>
       <c r="B224" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C224" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -10590,10 +10596,10 @@
         <v>338</v>
       </c>
       <c r="B225" t="s">
+        <v>720</v>
+      </c>
+      <c r="C225" t="s">
         <v>721</v>
-      </c>
-      <c r="C225" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -10601,10 +10607,10 @@
         <v>338</v>
       </c>
       <c r="B226" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C226" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -10612,10 +10618,10 @@
         <v>338</v>
       </c>
       <c r="B227" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C227" t="s">
-        <v>706</v>
+        <v>785</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -10623,10 +10629,10 @@
         <v>338</v>
       </c>
       <c r="B228" t="s">
+        <v>724</v>
+      </c>
+      <c r="C228" t="s">
         <v>725</v>
-      </c>
-      <c r="C228" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -10637,7 +10643,7 @@
         <v>530</v>
       </c>
       <c r="C229" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -10645,7 +10651,7 @@
         <v>338</v>
       </c>
       <c r="B230" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C230" t="s">
         <v>513</v>
@@ -10843,7 +10849,7 @@
         <v>291</v>
       </c>
       <c r="B248" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C248" t="s">
         <v>551</v>
@@ -10854,7 +10860,7 @@
         <v>291</v>
       </c>
       <c r="B249" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C249" t="s">
         <v>551</v>
@@ -10865,7 +10871,7 @@
         <v>291</v>
       </c>
       <c r="B250" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C250" t="s">
         <v>633</v>
@@ -10876,7 +10882,7 @@
         <v>291</v>
       </c>
       <c r="B251" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C251" t="s">
         <v>543</v>
@@ -10887,7 +10893,7 @@
         <v>291</v>
       </c>
       <c r="B252" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C252" t="s">
         <v>549</v>
@@ -10898,7 +10904,7 @@
         <v>291</v>
       </c>
       <c r="B253" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C253" t="s">
         <v>549</v>
@@ -10909,7 +10915,7 @@
         <v>291</v>
       </c>
       <c r="B254" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C254" t="s">
         <v>543</v>
@@ -10931,7 +10937,7 @@
         <v>291</v>
       </c>
       <c r="B256" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C256" t="s">
         <v>545</v>
@@ -10942,7 +10948,7 @@
         <v>291</v>
       </c>
       <c r="B257" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C257" t="s">
         <v>554</v>
@@ -10953,7 +10959,7 @@
         <v>291</v>
       </c>
       <c r="B258" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C258" t="s">
         <v>554</v>
@@ -10964,7 +10970,7 @@
         <v>291</v>
       </c>
       <c r="B259" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C259" t="s">
         <v>554</v>
@@ -10975,10 +10981,10 @@
         <v>291</v>
       </c>
       <c r="B260" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C260" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -10986,10 +10992,10 @@
         <v>291</v>
       </c>
       <c r="B261" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C261" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -10997,10 +11003,10 @@
         <v>291</v>
       </c>
       <c r="B262" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C262" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -11008,10 +11014,10 @@
         <v>291</v>
       </c>
       <c r="B263" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C263" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -11019,10 +11025,10 @@
         <v>291</v>
       </c>
       <c r="B264" t="s">
+        <v>743</v>
+      </c>
+      <c r="C264" t="s">
         <v>744</v>
-      </c>
-      <c r="C264" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -11033,7 +11039,7 @@
         <v>443</v>
       </c>
       <c r="C265" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -11044,7 +11050,7 @@
         <v>445</v>
       </c>
       <c r="C266" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -11052,10 +11058,10 @@
         <v>377</v>
       </c>
       <c r="B267" t="s">
+        <v>747</v>
+      </c>
+      <c r="C267" t="s">
         <v>748</v>
-      </c>
-      <c r="C267" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -11063,7 +11069,7 @@
         <v>377</v>
       </c>
       <c r="B268" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C268" t="s">
         <v>488</v>
@@ -11074,7 +11080,7 @@
         <v>377</v>
       </c>
       <c r="B269" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C269" t="s">
         <v>455</v>
@@ -11085,10 +11091,10 @@
         <v>377</v>
       </c>
       <c r="B270" t="s">
+        <v>751</v>
+      </c>
+      <c r="C270" t="s">
         <v>752</v>
-      </c>
-      <c r="C270" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -11096,7 +11102,7 @@
         <v>377</v>
       </c>
       <c r="B271" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C271" t="s">
         <v>459</v>
@@ -11118,10 +11124,10 @@
         <v>377</v>
       </c>
       <c r="B273" t="s">
+        <v>754</v>
+      </c>
+      <c r="C273" t="s">
         <v>755</v>
-      </c>
-      <c r="C273" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -11129,10 +11135,10 @@
         <v>377</v>
       </c>
       <c r="B274" t="s">
+        <v>756</v>
+      </c>
+      <c r="C274" t="s">
         <v>757</v>
-      </c>
-      <c r="C274" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -11143,7 +11149,7 @@
         <v>443</v>
       </c>
       <c r="C275" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -11154,7 +11160,7 @@
         <v>445</v>
       </c>
       <c r="C276" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -11162,10 +11168,10 @@
         <v>403</v>
       </c>
       <c r="B277" t="s">
+        <v>747</v>
+      </c>
+      <c r="C277" t="s">
         <v>748</v>
-      </c>
-      <c r="C277" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -11173,7 +11179,7 @@
         <v>403</v>
       </c>
       <c r="B278" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C278" t="s">
         <v>488</v>
@@ -11184,7 +11190,7 @@
         <v>403</v>
       </c>
       <c r="B279" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C279" t="s">
         <v>455</v>
@@ -11195,10 +11201,10 @@
         <v>403</v>
       </c>
       <c r="B280" t="s">
+        <v>751</v>
+      </c>
+      <c r="C280" t="s">
         <v>752</v>
-      </c>
-      <c r="C280" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -11206,7 +11212,7 @@
         <v>403</v>
       </c>
       <c r="B281" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C281" t="s">
         <v>459</v>
@@ -11228,10 +11234,10 @@
         <v>403</v>
       </c>
       <c r="B283" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C283" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -11239,10 +11245,10 @@
         <v>403</v>
       </c>
       <c r="B284" t="s">
+        <v>756</v>
+      </c>
+      <c r="C284" t="s">
         <v>757</v>
-      </c>
-      <c r="C284" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -11250,7 +11256,7 @@
         <v>424</v>
       </c>
       <c r="B285" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C285" t="s">
         <v>453</v>
@@ -11261,7 +11267,7 @@
         <v>424</v>
       </c>
       <c r="B286" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C286" t="s">
         <v>702</v>
@@ -11272,7 +11278,7 @@
         <v>424</v>
       </c>
       <c r="B287" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C287" t="s">
         <v>448</v>
@@ -11283,10 +11289,10 @@
         <v>424</v>
       </c>
       <c r="B288" t="s">
+        <v>762</v>
+      </c>
+      <c r="C288" t="s">
         <v>763</v>
-      </c>
-      <c r="C288" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -11294,7 +11300,7 @@
         <v>424</v>
       </c>
       <c r="B289" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C289" t="s">
         <v>501</v>
@@ -11308,7 +11314,7 @@
         <v>3</v>
       </c>
       <c r="C290" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -11316,7 +11322,7 @@
         <v>424</v>
       </c>
       <c r="B291" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C291" t="s">
         <v>461</v>
@@ -11327,10 +11333,10 @@
         <v>424</v>
       </c>
       <c r="B292" t="s">
+        <v>767</v>
+      </c>
+      <c r="C292" t="s">
         <v>768</v>
-      </c>
-      <c r="C292" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -11338,10 +11344,10 @@
         <v>424</v>
       </c>
       <c r="B293" t="s">
+        <v>769</v>
+      </c>
+      <c r="C293" t="s">
         <v>770</v>
-      </c>
-      <c r="C293" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -11349,7 +11355,7 @@
         <v>424</v>
       </c>
       <c r="B294" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C294" t="s">
         <v>497</v>
@@ -11360,7 +11366,7 @@
         <v>424</v>
       </c>
       <c r="B295" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C295" t="s">
         <v>504</v>
@@ -11371,7 +11377,7 @@
         <v>424</v>
       </c>
       <c r="B296" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C296" t="s">
         <v>497</v>
@@ -11382,10 +11388,10 @@
         <v>424</v>
       </c>
       <c r="B297" t="s">
+        <v>774</v>
+      </c>
+      <c r="C297" t="s">
         <v>775</v>
-      </c>
-      <c r="C297" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -11393,7 +11399,7 @@
         <v>424</v>
       </c>
       <c r="B298" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C298" t="s">
         <v>585</v>
@@ -11415,7 +11421,7 @@
         <v>424</v>
       </c>
       <c r="B300" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C300" t="s">
         <v>478</v>
@@ -11426,7 +11432,7 @@
         <v>424</v>
       </c>
       <c r="B301" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C301" t="s">
         <v>480</v>
@@ -11437,7 +11443,7 @@
         <v>424</v>
       </c>
       <c r="B302" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C302" t="s">
         <v>585</v>
@@ -11448,10 +11454,10 @@
         <v>424</v>
       </c>
       <c r="B303" t="s">
+        <v>780</v>
+      </c>
+      <c r="C303" t="s">
         <v>781</v>
-      </c>
-      <c r="C303" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -11470,10 +11476,10 @@
         <v>424</v>
       </c>
       <c r="B305" t="s">
+        <v>782</v>
+      </c>
+      <c r="C305" t="s">
         <v>783</v>
-      </c>
-      <c r="C305" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -11481,14 +11487,14 @@
         <v>424</v>
       </c>
       <c r="B306" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C306" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C108" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <autoFilter ref="A1:C306" xr:uid="{00000000-0001-0000-0300-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C108">
       <sortCondition ref="A1:A108"/>
     </sortState>

--- a/Base.xlsx
+++ b/Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LK\Desktop\GItHubUpload\EVALUATION-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D8DC1A-8C4E-4DE2-8C1D-34498E0EEC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D874CBA-9689-4E86-AD68-72D55F392B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste" sheetId="3" r:id="rId1"/>
@@ -18,13 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Classification!$A$1:$C$306</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Liste!$A$1:$C$418</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="787">
   <si>
     <t>Classe</t>
   </si>
@@ -261,9 +262,6 @@
   </si>
   <si>
     <t>DJIKI Huguette</t>
-  </si>
-  <si>
-    <t>11TSS06</t>
   </si>
   <si>
     <t>DJITUPURI Emmanuel</t>
@@ -4264,11 +4262,11 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="95" t="s">
+      <c r="A69" s="95">
+        <v>110006</v>
+      </c>
+      <c r="B69" s="125" t="s">
         <v>79</v>
-      </c>
-      <c r="B69" s="125" t="s">
-        <v>80</v>
       </c>
       <c r="C69" t="s">
         <v>73</v>
@@ -4279,7 +4277,7 @@
         <v>25002</v>
       </c>
       <c r="B70" s="125" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C70" t="s">
         <v>73</v>
@@ -4290,7 +4288,7 @@
         <v>23074</v>
       </c>
       <c r="B71" s="125" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C71" t="s">
         <v>73</v>
@@ -4301,7 +4299,7 @@
         <v>23075</v>
       </c>
       <c r="B72" s="125" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C72" t="s">
         <v>73</v>
@@ -4312,7 +4310,7 @@
         <v>23076</v>
       </c>
       <c r="B73" s="125" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C73" t="s">
         <v>73</v>
@@ -4323,7 +4321,7 @@
         <v>23078</v>
       </c>
       <c r="B74" s="125" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C74" t="s">
         <v>73</v>
@@ -4334,7 +4332,7 @@
         <v>23079</v>
       </c>
       <c r="B75" s="125" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C75" t="s">
         <v>73</v>
@@ -4345,7 +4343,7 @@
         <v>23080</v>
       </c>
       <c r="B76" s="125" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C76" t="s">
         <v>73</v>
@@ -4356,7 +4354,7 @@
         <v>23081</v>
       </c>
       <c r="B77" s="125" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C77" t="s">
         <v>73</v>
@@ -4367,7 +4365,7 @@
         <v>23082</v>
       </c>
       <c r="B78" s="125" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C78" t="s">
         <v>73</v>
@@ -4378,7 +4376,7 @@
         <v>23083</v>
       </c>
       <c r="B79" s="125" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C79" t="s">
         <v>73</v>
@@ -4389,7 +4387,7 @@
         <v>23086</v>
       </c>
       <c r="B80" s="125" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C80" t="s">
         <v>73</v>
@@ -4400,7 +4398,7 @@
         <v>23087</v>
       </c>
       <c r="B81" s="125" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C81" t="s">
         <v>73</v>
@@ -4411,10 +4409,10 @@
         <v>23088</v>
       </c>
       <c r="B82" s="127" t="s">
+        <v>92</v>
+      </c>
+      <c r="C82" s="92" t="s">
         <v>93</v>
-      </c>
-      <c r="C82" s="92" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -4422,10 +4420,10 @@
         <v>23089</v>
       </c>
       <c r="B83" s="125" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C83" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -4433,10 +4431,10 @@
         <v>23090</v>
       </c>
       <c r="B84" s="125" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -4444,10 +4442,10 @@
         <v>14102</v>
       </c>
       <c r="B85" s="125" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C85" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -4455,10 +4453,10 @@
         <v>23091</v>
       </c>
       <c r="B86" s="125" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C86" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -4466,10 +4464,10 @@
         <v>23092</v>
       </c>
       <c r="B87" s="125" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C87" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -4477,10 +4475,10 @@
         <v>25082</v>
       </c>
       <c r="B88" s="125" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C88" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -4488,10 +4486,10 @@
         <v>23093</v>
       </c>
       <c r="B89" s="125" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C89" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -4499,10 +4497,10 @@
         <v>23095</v>
       </c>
       <c r="B90" s="125" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C90" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -4510,10 +4508,10 @@
         <v>23096</v>
       </c>
       <c r="B91" s="125" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C91" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -4521,10 +4519,10 @@
         <v>22062</v>
       </c>
       <c r="B92" s="125" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C92" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -4532,10 +4530,10 @@
         <v>23099</v>
       </c>
       <c r="B93" s="125" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -4543,10 +4541,10 @@
         <v>23101</v>
       </c>
       <c r="B94" s="125" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C94" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4554,10 +4552,10 @@
         <v>25040</v>
       </c>
       <c r="B95" s="128" t="s">
+        <v>106</v>
+      </c>
+      <c r="C95" s="92" t="s">
         <v>107</v>
-      </c>
-      <c r="C95" s="92" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4565,10 +4563,10 @@
         <v>24046</v>
       </c>
       <c r="B96" s="129" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4576,10 +4574,10 @@
         <v>25042</v>
       </c>
       <c r="B97" s="129" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C97" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4587,10 +4585,10 @@
         <v>25043</v>
       </c>
       <c r="B98" s="129" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4598,10 +4596,10 @@
         <v>25044</v>
       </c>
       <c r="B99" s="129" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C99" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4609,10 +4607,10 @@
         <v>24124</v>
       </c>
       <c r="B100" s="129" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C100" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4620,10 +4618,10 @@
         <v>25045</v>
       </c>
       <c r="B101" s="129" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C101" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4631,10 +4629,10 @@
         <v>25047</v>
       </c>
       <c r="B102" s="129" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C102" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4642,10 +4640,10 @@
         <v>25048</v>
       </c>
       <c r="B103" s="129" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C103" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4653,10 +4651,10 @@
         <v>25049</v>
       </c>
       <c r="B104" s="129" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4664,10 +4662,10 @@
         <v>25050</v>
       </c>
       <c r="B105" s="129" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C105" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4675,10 +4673,10 @@
         <v>25051</v>
       </c>
       <c r="B106" s="129" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C106" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4686,10 +4684,10 @@
         <v>25052</v>
       </c>
       <c r="B107" s="129" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C107" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4697,10 +4695,10 @@
         <v>25053</v>
       </c>
       <c r="B108" s="129" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C108" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4708,10 +4706,10 @@
         <v>25054</v>
       </c>
       <c r="B109" s="129" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C109" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4719,10 +4717,10 @@
         <v>25055</v>
       </c>
       <c r="B110" s="129" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C110" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4730,10 +4728,10 @@
         <v>25056</v>
       </c>
       <c r="B111" s="129" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C111" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4741,10 +4739,10 @@
         <v>25057</v>
       </c>
       <c r="B112" s="129" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C112" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4752,10 +4750,10 @@
         <v>25058</v>
       </c>
       <c r="B113" s="129" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C113" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4763,10 +4761,10 @@
         <v>25059</v>
       </c>
       <c r="B114" s="129" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4774,10 +4772,10 @@
         <v>25061</v>
       </c>
       <c r="B115" s="129" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C115" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4785,10 +4783,10 @@
         <v>25062</v>
       </c>
       <c r="B116" s="129" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C116" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4796,10 +4794,10 @@
         <v>25063</v>
       </c>
       <c r="B117" s="129" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C117" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4807,10 +4805,10 @@
         <v>25065</v>
       </c>
       <c r="B118" s="129" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C118" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4818,10 +4816,10 @@
         <v>25068</v>
       </c>
       <c r="B119" s="129" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C119" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4829,10 +4827,10 @@
         <v>25069</v>
       </c>
       <c r="B120" s="129" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C120" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4840,10 +4838,10 @@
         <v>25070</v>
       </c>
       <c r="B121" s="129" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C121" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4851,10 +4849,10 @@
         <v>25072</v>
       </c>
       <c r="B122" s="130" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C122" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -4862,10 +4860,10 @@
         <v>25073</v>
       </c>
       <c r="B123" s="130" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C123" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -4873,10 +4871,10 @@
         <v>24047</v>
       </c>
       <c r="B124" s="126" t="s">
+        <v>136</v>
+      </c>
+      <c r="C124" s="92" t="s">
         <v>137</v>
-      </c>
-      <c r="C124" s="92" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -4884,10 +4882,10 @@
         <v>24048</v>
       </c>
       <c r="B125" s="90" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C125" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -4895,10 +4893,10 @@
         <v>24050</v>
       </c>
       <c r="B126" s="90" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C126" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -4906,10 +4904,10 @@
         <v>24051</v>
       </c>
       <c r="B127" s="90" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C127" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -4917,10 +4915,10 @@
         <v>24052</v>
       </c>
       <c r="B128" s="90" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C128" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -4928,10 +4926,10 @@
         <v>24053</v>
       </c>
       <c r="B129" s="90" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C129" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -4939,10 +4937,10 @@
         <v>24055</v>
       </c>
       <c r="B130" s="90" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C130" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -4950,10 +4948,10 @@
         <v>24056</v>
       </c>
       <c r="B131" s="90" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C131" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -4961,10 +4959,10 @@
         <v>24057</v>
       </c>
       <c r="B132" s="90" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C132" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -4972,10 +4970,10 @@
         <v>24058</v>
       </c>
       <c r="B133" s="90" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C133" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -4983,10 +4981,10 @@
         <v>24059</v>
       </c>
       <c r="B134" s="90" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C134" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -4994,10 +4992,10 @@
         <v>24060</v>
       </c>
       <c r="B135" s="90" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C135" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5005,10 +5003,10 @@
         <v>24061</v>
       </c>
       <c r="B136" s="90" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C136" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5016,10 +5014,10 @@
         <v>24062</v>
       </c>
       <c r="B137" s="90" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C137" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5027,10 +5025,10 @@
         <v>24063</v>
       </c>
       <c r="B138" s="90" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C138" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5038,10 +5036,10 @@
         <v>24064</v>
       </c>
       <c r="B139" s="90" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C139" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5049,10 +5047,10 @@
         <v>24065</v>
       </c>
       <c r="B140" s="90" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C140" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5060,10 +5058,10 @@
         <v>24066</v>
       </c>
       <c r="B141" s="90" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C141" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5071,10 +5069,10 @@
         <v>23050</v>
       </c>
       <c r="B142" s="90" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C142" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5082,10 +5080,10 @@
         <v>24067</v>
       </c>
       <c r="B143" s="90" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C143" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5093,10 +5091,10 @@
         <v>24068</v>
       </c>
       <c r="B144" s="90" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C144" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5104,10 +5102,10 @@
         <v>24069</v>
       </c>
       <c r="B145" s="90" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C145" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5115,10 +5113,10 @@
         <v>24070</v>
       </c>
       <c r="B146" s="90" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C146" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5126,10 +5124,10 @@
         <v>23058</v>
       </c>
       <c r="B147" s="90" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C147" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5137,10 +5135,10 @@
         <v>24071</v>
       </c>
       <c r="B148" s="90" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C148" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5148,10 +5146,10 @@
         <v>24072</v>
       </c>
       <c r="B149" s="90" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C149" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5159,10 +5157,10 @@
         <v>24073</v>
       </c>
       <c r="B150" s="90" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C150" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5170,10 +5168,10 @@
         <v>24074</v>
       </c>
       <c r="B151" s="90" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C151" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5181,10 +5179,10 @@
         <v>24075</v>
       </c>
       <c r="B152" s="90" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C152" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5192,10 +5190,10 @@
         <v>24076</v>
       </c>
       <c r="B153" s="90" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C153" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -5203,10 +5201,10 @@
         <v>24079</v>
       </c>
       <c r="B154" s="90" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C154" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5214,10 +5212,10 @@
         <v>23039</v>
       </c>
       <c r="B155" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="C155" s="92" t="s">
         <v>169</v>
-      </c>
-      <c r="C155" s="92" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5225,10 +5223,10 @@
         <v>23040</v>
       </c>
       <c r="B156" s="132" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C156" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5236,10 +5234,10 @@
         <v>23041</v>
       </c>
       <c r="B157" s="132" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C157" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5247,10 +5245,10 @@
         <v>23042</v>
       </c>
       <c r="B158" s="132" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C158" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5258,10 +5256,10 @@
         <v>23043</v>
       </c>
       <c r="B159" s="132" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C159" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5269,10 +5267,10 @@
         <v>23044</v>
       </c>
       <c r="B160" s="132" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C160" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5280,10 +5278,10 @@
         <v>23045</v>
       </c>
       <c r="B161" s="132" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C161" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5291,10 +5289,10 @@
         <v>22073</v>
       </c>
       <c r="B162" s="132" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C162" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5302,10 +5300,10 @@
         <v>23057</v>
       </c>
       <c r="B163" s="132" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C163" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5313,10 +5311,10 @@
         <v>23046</v>
       </c>
       <c r="B164" s="132" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C164" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5324,10 +5322,10 @@
         <v>23047</v>
       </c>
       <c r="B165" s="132" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C165" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5335,10 +5333,10 @@
         <v>23049</v>
       </c>
       <c r="B166" s="132" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C166" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5346,10 +5344,10 @@
         <v>23051</v>
       </c>
       <c r="B167" s="132" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C167" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5357,10 +5355,10 @@
         <v>23053</v>
       </c>
       <c r="B168" s="132" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C168" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5368,10 +5366,10 @@
         <v>23055</v>
       </c>
       <c r="B169" s="132" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C169" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5379,10 +5377,10 @@
         <v>23056</v>
       </c>
       <c r="B170" s="132" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C170" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5390,10 +5388,10 @@
         <v>23059</v>
       </c>
       <c r="B171" s="132" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C171" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5401,10 +5399,10 @@
         <v>23060</v>
       </c>
       <c r="B172" s="132" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C172" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5412,10 +5410,10 @@
         <v>23062</v>
       </c>
       <c r="B173" s="132" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C173" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5423,10 +5421,10 @@
         <v>23063</v>
       </c>
       <c r="B174" s="132" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C174" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5434,10 +5432,10 @@
         <v>23064</v>
       </c>
       <c r="B175" s="132" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C175" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5445,10 +5443,10 @@
         <v>23065</v>
       </c>
       <c r="B176" s="132" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C176" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
@@ -5456,10 +5454,10 @@
         <v>23067</v>
       </c>
       <c r="B177" s="132" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C177" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -5467,10 +5465,10 @@
         <v>24094</v>
       </c>
       <c r="B178" s="133" t="s">
+        <v>192</v>
+      </c>
+      <c r="C178" s="92" t="s">
         <v>193</v>
-      </c>
-      <c r="C178" s="92" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -5478,10 +5476,10 @@
         <v>22067</v>
       </c>
       <c r="B179" s="134" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C179" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -5489,10 +5487,10 @@
         <v>21001</v>
       </c>
       <c r="B180" s="135" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C180" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -5500,10 +5498,10 @@
         <v>18093</v>
       </c>
       <c r="B181" s="135" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C181" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -5511,10 +5509,10 @@
         <v>22068</v>
       </c>
       <c r="B182" s="134" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C182" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -5522,10 +5520,10 @@
         <v>23001</v>
       </c>
       <c r="B183" s="135" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C183" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -5533,10 +5531,10 @@
         <v>21002</v>
       </c>
       <c r="B184" s="135" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C184" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -5544,10 +5542,10 @@
         <v>24097</v>
       </c>
       <c r="B185" s="136" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C185" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -5555,10 +5553,10 @@
         <v>21003</v>
       </c>
       <c r="B186" s="135" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C186" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -5566,10 +5564,10 @@
         <v>22069</v>
       </c>
       <c r="B187" s="134" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C187" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -5577,10 +5575,10 @@
         <v>24098</v>
       </c>
       <c r="B188" s="136" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C188" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -5588,10 +5586,10 @@
         <v>22070</v>
       </c>
       <c r="B189" s="134" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C189" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -5599,10 +5597,10 @@
         <v>24081</v>
       </c>
       <c r="B190" s="135" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C190" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -5610,10 +5608,10 @@
         <v>21007</v>
       </c>
       <c r="B191" s="135" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C191" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -5621,10 +5619,10 @@
         <v>24082</v>
       </c>
       <c r="B192" s="137" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C192" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -5632,10 +5630,10 @@
         <v>22071</v>
       </c>
       <c r="B193" s="134" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C193" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -5643,10 +5641,10 @@
         <v>22072</v>
       </c>
       <c r="B194" s="138" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C194" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -5654,10 +5652,10 @@
         <v>19028</v>
       </c>
       <c r="B195" s="135" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C195" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -5665,10 +5663,10 @@
         <v>24084</v>
       </c>
       <c r="B196" s="137" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C196" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -5676,10 +5674,10 @@
         <v>22074</v>
       </c>
       <c r="B197" s="138" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C197" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -5687,10 +5685,10 @@
         <v>19029</v>
       </c>
       <c r="B198" s="135" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C198" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -5698,10 +5696,10 @@
         <v>20010</v>
       </c>
       <c r="B199" s="135" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C199" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -5709,10 +5707,10 @@
         <v>24101</v>
       </c>
       <c r="B200" s="139" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C200" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -5720,10 +5718,10 @@
         <v>20091</v>
       </c>
       <c r="B201" s="134" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C201" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -5731,10 +5729,10 @@
         <v>24102</v>
       </c>
       <c r="B202" s="136" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C202" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -5742,10 +5740,10 @@
         <v>24087</v>
       </c>
       <c r="B203" s="135" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C203" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -5753,10 +5751,10 @@
         <v>24088</v>
       </c>
       <c r="B204" s="135" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C204" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -5764,10 +5762,10 @@
         <v>24103</v>
       </c>
       <c r="B205" s="136" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C205" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -5775,10 +5773,10 @@
         <v>22076</v>
       </c>
       <c r="B206" s="134" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C206" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -5786,10 +5784,10 @@
         <v>22077</v>
       </c>
       <c r="B207" s="134" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C207" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -5797,10 +5795,10 @@
         <v>24104</v>
       </c>
       <c r="B208" s="136" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C208" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -5808,10 +5806,10 @@
         <v>24105</v>
       </c>
       <c r="B209" s="136" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C209" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -5819,10 +5817,10 @@
         <v>24089</v>
       </c>
       <c r="B210" s="135" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C210" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -5830,10 +5828,10 @@
         <v>22078</v>
       </c>
       <c r="B211" s="134" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C211" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -5841,10 +5839,10 @@
         <v>22079</v>
       </c>
       <c r="B212" s="134" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C212" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -5852,10 +5850,10 @@
         <v>24106</v>
       </c>
       <c r="B213" s="136" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C213" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -5863,10 +5861,10 @@
         <v>22080</v>
       </c>
       <c r="B214" s="134" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C214" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -5874,10 +5872,10 @@
         <v>24107</v>
       </c>
       <c r="B215" s="136" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C215" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -5885,10 +5883,10 @@
         <v>20089</v>
       </c>
       <c r="B216" s="135" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C216" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -5896,10 +5894,10 @@
         <v>24108</v>
       </c>
       <c r="B217" s="139" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C217" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -5907,10 +5905,10 @@
         <v>23025</v>
       </c>
       <c r="B218" s="135" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C218" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -5918,10 +5916,10 @@
         <v>22081</v>
       </c>
       <c r="B219" s="134" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C219" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -5929,10 +5927,10 @@
         <v>22093</v>
       </c>
       <c r="B220" s="134" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C220" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -5940,10 +5938,10 @@
         <v>22082</v>
       </c>
       <c r="B221" s="134" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C221" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -5951,10 +5949,10 @@
         <v>23026</v>
       </c>
       <c r="B222" s="135" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C222" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -5962,10 +5960,10 @@
         <v>24109</v>
       </c>
       <c r="B223" s="136" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C223" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -5973,10 +5971,10 @@
         <v>22084</v>
       </c>
       <c r="B224" s="138" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C224" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -5984,10 +5982,10 @@
         <v>24110</v>
       </c>
       <c r="B225" s="136" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C225" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -5995,10 +5993,10 @@
         <v>24111</v>
       </c>
       <c r="B226" s="136" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C226" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -6006,10 +6004,10 @@
         <v>24112</v>
       </c>
       <c r="B227" s="139" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C227" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -6017,10 +6015,10 @@
         <v>24113</v>
       </c>
       <c r="B228" s="139" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C228" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -6028,10 +6026,10 @@
         <v>24090</v>
       </c>
       <c r="B229" s="135" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C229" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -6039,10 +6037,10 @@
         <v>22085</v>
       </c>
       <c r="B230" s="134" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C230" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -6050,10 +6048,10 @@
         <v>21017</v>
       </c>
       <c r="B231" s="135" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C231" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -6061,10 +6059,10 @@
         <v>23008</v>
       </c>
       <c r="B232" s="135" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C232" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -6072,10 +6070,10 @@
         <v>24091</v>
       </c>
       <c r="B233" s="135" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C233" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -6083,10 +6081,10 @@
         <v>24092</v>
       </c>
       <c r="B234" s="135" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C234" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -6094,10 +6092,10 @@
         <v>23009</v>
       </c>
       <c r="B235" s="135" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C235" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -6105,10 +6103,10 @@
         <v>24114</v>
       </c>
       <c r="B236" s="136" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C236" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -6116,10 +6114,10 @@
         <v>21019</v>
       </c>
       <c r="B237" s="135" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C237" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -6127,10 +6125,10 @@
         <v>24115</v>
       </c>
       <c r="B238" s="136" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C238" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -6138,10 +6136,10 @@
         <v>22086</v>
       </c>
       <c r="B239" s="134" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C239" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -6149,10 +6147,10 @@
         <v>22087</v>
       </c>
       <c r="B240" s="134" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C240" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -6160,10 +6158,10 @@
         <v>22088</v>
       </c>
       <c r="B241" s="134" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C241" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -6171,10 +6169,10 @@
         <v>22089</v>
       </c>
       <c r="B242" s="138" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C242" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -6182,10 +6180,10 @@
         <v>24118</v>
       </c>
       <c r="B243" s="139" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C243" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -6193,10 +6191,10 @@
         <v>24119</v>
       </c>
       <c r="B244" s="136" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C244" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -6204,10 +6202,10 @@
         <v>22090</v>
       </c>
       <c r="B245" s="138" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C245" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -6215,10 +6213,10 @@
         <v>22091</v>
       </c>
       <c r="B246" s="138" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -6226,10 +6224,10 @@
         <v>25090</v>
       </c>
       <c r="B247" s="133" t="s">
+        <v>262</v>
+      </c>
+      <c r="C247" s="92" t="s">
         <v>263</v>
-      </c>
-      <c r="C247" s="92" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -6237,10 +6235,10 @@
         <v>25091</v>
       </c>
       <c r="B248" s="136" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C248" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -6248,10 +6246,10 @@
         <v>25092</v>
       </c>
       <c r="B249" s="136" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C249" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -6259,10 +6257,10 @@
         <v>25093</v>
       </c>
       <c r="B250" s="136" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C250" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -6270,10 +6268,10 @@
         <v>25095</v>
       </c>
       <c r="B251" s="136" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C251" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -6281,10 +6279,10 @@
         <v>25096</v>
       </c>
       <c r="B252" s="136" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C252" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -6292,10 +6290,10 @@
         <v>24099</v>
       </c>
       <c r="B253" s="136" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C253" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -6303,10 +6301,10 @@
         <v>25097</v>
       </c>
       <c r="B254" s="136" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C254" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -6314,10 +6312,10 @@
         <v>25098</v>
       </c>
       <c r="B255" s="136" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C255" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -6325,10 +6323,10 @@
         <v>24100</v>
       </c>
       <c r="B256" s="136" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C256" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -6336,10 +6334,10 @@
         <v>25100</v>
       </c>
       <c r="B257" s="140" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C257" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -6347,10 +6345,10 @@
         <v>25101</v>
       </c>
       <c r="B258" s="136" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C258" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -6358,10 +6356,10 @@
         <v>25102</v>
       </c>
       <c r="B259" s="136" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C259" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -6369,10 +6367,10 @@
         <v>25103</v>
       </c>
       <c r="B260" s="136" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C260" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -6380,10 +6378,10 @@
         <v>25105</v>
       </c>
       <c r="B261" s="136" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C261" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -6391,10 +6389,10 @@
         <v>25106</v>
       </c>
       <c r="B262" s="136" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C262" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -6402,10 +6400,10 @@
         <v>25107</v>
       </c>
       <c r="B263" s="136" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C263" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -6413,10 +6411,10 @@
         <v>25110</v>
       </c>
       <c r="B264" s="136" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C264" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -6424,10 +6422,10 @@
         <v>25111</v>
       </c>
       <c r="B265" s="136" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C265" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -6435,10 +6433,10 @@
         <v>25112</v>
       </c>
       <c r="B266" s="136" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C266" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -6446,10 +6444,10 @@
         <v>25113</v>
       </c>
       <c r="B267" s="136" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C267" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -6457,10 +6455,10 @@
         <v>25116</v>
       </c>
       <c r="B268" s="136" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C268" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -6468,10 +6466,10 @@
         <v>25118</v>
       </c>
       <c r="B269" s="136" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C269" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -6479,10 +6477,10 @@
         <v>25120</v>
       </c>
       <c r="B270" s="136" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C270" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -6490,10 +6488,10 @@
         <v>25122</v>
       </c>
       <c r="B271" s="136" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C271" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -6501,10 +6499,10 @@
         <v>25123</v>
       </c>
       <c r="B272" s="136" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C272" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -6512,10 +6510,10 @@
         <v>21023</v>
       </c>
       <c r="B273" s="141" t="s">
+        <v>289</v>
+      </c>
+      <c r="C273" s="92" t="s">
         <v>290</v>
-      </c>
-      <c r="C273" s="92" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -6523,10 +6521,10 @@
         <v>22001</v>
       </c>
       <c r="B274" s="142" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C274" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -6534,10 +6532,10 @@
         <v>21024</v>
       </c>
       <c r="B275" s="142" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C275" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -6545,10 +6543,10 @@
         <v>23018</v>
       </c>
       <c r="B276" s="142" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C276" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -6556,10 +6554,10 @@
         <v>22003</v>
       </c>
       <c r="B277" s="142" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C277" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -6567,10 +6565,10 @@
         <v>23002</v>
       </c>
       <c r="B278" s="142" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C278" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -6578,10 +6576,10 @@
         <v>22026</v>
       </c>
       <c r="B279" s="142" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C279" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -6589,10 +6587,10 @@
         <v>20024</v>
       </c>
       <c r="B280" s="142" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C280" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -6600,10 +6598,10 @@
         <v>23006</v>
       </c>
       <c r="B281" s="142" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C281" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -6611,10 +6609,10 @@
         <v>22006</v>
       </c>
       <c r="B282" s="142" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C282" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -6622,10 +6620,10 @@
         <v>21029</v>
       </c>
       <c r="B283" s="142" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C283" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -6633,10 +6631,10 @@
         <v>23023</v>
       </c>
       <c r="B284" s="142" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C284" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -6644,10 +6642,10 @@
         <v>23027</v>
       </c>
       <c r="B285" s="142" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C285" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -6655,10 +6653,10 @@
         <v>23028</v>
       </c>
       <c r="B286" s="142" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C286" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -6666,10 +6664,10 @@
         <v>22025</v>
       </c>
       <c r="B287" s="142" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C287" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -6677,10 +6675,10 @@
         <v>21031</v>
       </c>
       <c r="B288" s="142" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C288" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -6688,10 +6686,10 @@
         <v>23031</v>
       </c>
       <c r="B289" s="142" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C289" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -6699,10 +6697,10 @@
         <v>21034</v>
       </c>
       <c r="B290" s="142" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C290" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -6710,10 +6708,10 @@
         <v>22018</v>
       </c>
       <c r="B291" s="142" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C291" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -6721,10 +6719,10 @@
         <v>22019</v>
       </c>
       <c r="B292" s="142" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C292" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -6732,10 +6730,10 @@
         <v>20025</v>
       </c>
       <c r="B293" s="142" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C293" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -6743,10 +6741,10 @@
         <v>21022</v>
       </c>
       <c r="B294" s="143" t="s">
+        <v>311</v>
+      </c>
+      <c r="C294" s="92" t="s">
         <v>312</v>
-      </c>
-      <c r="C294" s="92" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -6754,10 +6752,10 @@
         <v>21025</v>
       </c>
       <c r="B295" s="135" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C295" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -6765,10 +6763,10 @@
         <v>23015</v>
       </c>
       <c r="B296" s="135" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C296" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -6776,10 +6774,10 @@
         <v>23004</v>
       </c>
       <c r="B297" s="135" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C297" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -6787,10 +6785,10 @@
         <v>22004</v>
       </c>
       <c r="B298" s="135" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C298" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -6798,10 +6796,10 @@
         <v>23005</v>
       </c>
       <c r="B299" s="135" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C299" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -6809,10 +6807,10 @@
         <v>21026</v>
       </c>
       <c r="B300" s="135" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C300" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -6820,10 +6818,10 @@
         <v>22005</v>
       </c>
       <c r="B301" s="135" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C301" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -6831,10 +6829,10 @@
         <v>22075</v>
       </c>
       <c r="B302" s="135" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C302" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -6842,10 +6840,10 @@
         <v>21011</v>
       </c>
       <c r="B303" s="135" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C303" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -6853,10 +6851,10 @@
         <v>23020</v>
       </c>
       <c r="B304" s="135" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C304" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -6864,10 +6862,10 @@
         <v>21030</v>
       </c>
       <c r="B305" s="135" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C305" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -6875,10 +6873,10 @@
         <v>22011</v>
       </c>
       <c r="B306" s="135" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C306" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -6886,10 +6884,10 @@
         <v>22034</v>
       </c>
       <c r="B307" s="135" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C307" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -6897,10 +6895,10 @@
         <v>22012</v>
       </c>
       <c r="B308" s="135" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C308" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -6908,10 +6906,10 @@
         <v>18080</v>
       </c>
       <c r="B309" s="135" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C309" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -6919,10 +6917,10 @@
         <v>22014</v>
       </c>
       <c r="B310" s="135" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C310" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -6930,10 +6928,10 @@
         <v>23007</v>
       </c>
       <c r="B311" s="135" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C311" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -6941,10 +6939,10 @@
         <v>21035</v>
       </c>
       <c r="B312" s="135" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C312" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -6952,10 +6950,10 @@
         <v>23012</v>
       </c>
       <c r="B313" s="135" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C313" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -6963,10 +6961,10 @@
         <v>23013</v>
       </c>
       <c r="B314" s="135" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C314" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -6974,10 +6972,10 @@
         <v>22017</v>
       </c>
       <c r="B315" s="135" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C315" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -6985,10 +6983,10 @@
         <v>20072</v>
       </c>
       <c r="B316" s="135" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C316" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6996,10 +6994,10 @@
         <v>21040</v>
       </c>
       <c r="B317" s="135" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C317" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7007,10 +7005,10 @@
         <v>20080</v>
       </c>
       <c r="B318" s="144" t="s">
+        <v>336</v>
+      </c>
+      <c r="C318" s="92" t="s">
         <v>337</v>
-      </c>
-      <c r="C318" s="92" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7018,10 +7016,10 @@
         <v>23019</v>
       </c>
       <c r="B319" s="145" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C319" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7029,10 +7027,10 @@
         <v>23021</v>
       </c>
       <c r="B320" s="145" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C320" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7040,10 +7038,10 @@
         <v>21028</v>
       </c>
       <c r="B321" s="145" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C321" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7051,10 +7049,10 @@
         <v>23022</v>
       </c>
       <c r="B322" s="145" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C322" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7062,10 +7060,10 @@
         <v>23030</v>
       </c>
       <c r="B323" s="145" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C323" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7073,10 +7071,10 @@
         <v>21032</v>
       </c>
       <c r="B324" s="146" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C324" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7084,10 +7082,10 @@
         <v>23010</v>
       </c>
       <c r="B325" s="146" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C325" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7095,10 +7093,10 @@
         <v>23032</v>
       </c>
       <c r="B326" s="145" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C326" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7106,10 +7104,10 @@
         <v>21036</v>
       </c>
       <c r="B327" s="145" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C327" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7117,10 +7115,10 @@
         <v>23014</v>
       </c>
       <c r="B328" s="145" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C328" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="329" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7128,10 +7126,10 @@
         <v>23035</v>
       </c>
       <c r="B329" s="145" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C329" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7139,10 +7137,10 @@
         <v>25074</v>
       </c>
       <c r="B330" s="116" t="s">
+        <v>349</v>
+      </c>
+      <c r="C330" s="92" t="s">
         <v>350</v>
-      </c>
-      <c r="C330" s="92" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7150,10 +7148,10 @@
         <v>24080</v>
       </c>
       <c r="B331" s="118" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C331" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7161,10 +7159,10 @@
         <v>25075</v>
       </c>
       <c r="B332" s="118" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C332" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7172,10 +7170,10 @@
         <v>22046</v>
       </c>
       <c r="B333" s="120" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C333" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7183,10 +7181,10 @@
         <v>25076</v>
       </c>
       <c r="B334" s="120" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C334" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7194,10 +7192,10 @@
         <v>22047</v>
       </c>
       <c r="B335" s="120" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C335" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7205,10 +7203,10 @@
         <v>25077</v>
       </c>
       <c r="B336" s="120" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C336" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7216,10 +7214,10 @@
         <v>22052</v>
       </c>
       <c r="B337" s="120" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C337" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7227,10 +7225,10 @@
         <v>25078</v>
       </c>
       <c r="B338" s="120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C338" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7238,10 +7236,10 @@
         <v>25079</v>
       </c>
       <c r="B339" s="120" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C339" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7249,10 +7247,10 @@
         <v>24086</v>
       </c>
       <c r="B340" s="120" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C340" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7260,10 +7258,10 @@
         <v>25083</v>
       </c>
       <c r="B341" s="120" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C341" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7271,10 +7269,10 @@
         <v>25083</v>
       </c>
       <c r="B342" s="120" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C342" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7282,10 +7280,10 @@
         <v>22058</v>
       </c>
       <c r="B343" s="120" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C343" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7293,10 +7291,10 @@
         <v>22059</v>
       </c>
       <c r="B344" s="120" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C344" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="345" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7304,10 +7302,10 @@
         <v>25085</v>
       </c>
       <c r="B345" s="120" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C345" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7315,10 +7313,10 @@
         <v>20019</v>
       </c>
       <c r="B346" s="120" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C346" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7326,10 +7324,10 @@
         <v>22060</v>
       </c>
       <c r="B347" s="121" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C347" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7337,10 +7335,10 @@
         <v>25086</v>
       </c>
       <c r="B348" s="121" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C348" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7348,10 +7346,10 @@
         <v>25087</v>
       </c>
       <c r="B349" s="121" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C349" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7359,10 +7357,10 @@
         <v>22061</v>
       </c>
       <c r="B350" s="120" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C350" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7370,10 +7368,10 @@
         <v>18069</v>
       </c>
       <c r="B351" s="120" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C351" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7381,10 +7379,10 @@
         <v>24093</v>
       </c>
       <c r="B352" s="120" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C352" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7392,10 +7390,10 @@
         <v>22066</v>
       </c>
       <c r="B353" s="120" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C353" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7403,10 +7401,10 @@
         <v>25089</v>
       </c>
       <c r="B354" s="118" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C354" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
@@ -7414,10 +7412,10 @@
         <v>24144</v>
       </c>
       <c r="B355" s="147" t="s">
+        <v>375</v>
+      </c>
+      <c r="C355" s="92" t="s">
         <v>376</v>
-      </c>
-      <c r="C355" s="92" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
@@ -7425,10 +7423,10 @@
         <v>24123</v>
       </c>
       <c r="B356" s="148" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C356" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
@@ -7436,10 +7434,10 @@
         <v>25125</v>
       </c>
       <c r="B357" s="148" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C357" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
@@ -7447,10 +7445,10 @@
         <v>24129</v>
       </c>
       <c r="B358" s="148" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C358" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
@@ -7458,10 +7456,10 @@
         <v>25126</v>
       </c>
       <c r="B359" s="148" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C359" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
@@ -7469,10 +7467,10 @@
         <v>24134</v>
       </c>
       <c r="B360" s="148" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C360" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
@@ -7480,10 +7478,10 @@
         <v>25127</v>
       </c>
       <c r="B361" s="148" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C361" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
@@ -7491,10 +7489,10 @@
         <v>25128</v>
       </c>
       <c r="B362" s="148" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C362" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -7502,10 +7500,10 @@
         <v>25129</v>
       </c>
       <c r="B363" s="148" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C363" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
@@ -7513,10 +7511,10 @@
         <v>25130</v>
       </c>
       <c r="B364" s="148" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C364" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
@@ -7524,10 +7522,10 @@
         <v>25131</v>
       </c>
       <c r="B365" s="148" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C365" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
@@ -7535,10 +7533,10 @@
         <v>25132</v>
       </c>
       <c r="B366" s="148" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C366" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
@@ -7546,10 +7544,10 @@
         <v>24122</v>
       </c>
       <c r="B367" s="148" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C367" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
@@ -7557,10 +7555,10 @@
         <v>25133</v>
       </c>
       <c r="B368" s="148" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C368" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
@@ -7568,10 +7566,10 @@
         <v>24143</v>
       </c>
       <c r="B369" s="148" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C369" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
@@ -7579,10 +7577,10 @@
         <v>25134</v>
       </c>
       <c r="B370" s="148" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C370" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
@@ -7590,10 +7588,10 @@
         <v>24138</v>
       </c>
       <c r="B371" s="148" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C371" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
@@ -7601,10 +7599,10 @@
         <v>25135</v>
       </c>
       <c r="B372" s="148" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C372" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
@@ -7612,10 +7610,10 @@
         <v>25136</v>
       </c>
       <c r="B373" s="148" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C373" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -7623,10 +7621,10 @@
         <v>25137</v>
       </c>
       <c r="B374" s="148" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C374" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -7634,10 +7632,10 @@
         <v>25138</v>
       </c>
       <c r="B375" s="148" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C375" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -7645,10 +7643,10 @@
         <v>25141</v>
       </c>
       <c r="B376" s="148" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C376" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
@@ -7656,10 +7654,10 @@
         <v>24148</v>
       </c>
       <c r="B377" s="148" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C377" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -7667,10 +7665,10 @@
         <v>25139</v>
       </c>
       <c r="B378" s="148" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C378" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
@@ -7678,10 +7676,10 @@
         <v>25140</v>
       </c>
       <c r="B379" s="148" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C379" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7689,10 +7687,10 @@
         <v>25030</v>
       </c>
       <c r="B380" s="126" t="s">
+        <v>401</v>
+      </c>
+      <c r="C380" s="92" t="s">
         <v>402</v>
-      </c>
-      <c r="C380" s="92" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7700,10 +7698,10 @@
         <v>25007</v>
       </c>
       <c r="B381" s="90" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C381" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7711,10 +7709,10 @@
         <v>25011</v>
       </c>
       <c r="B382" s="90" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C382" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7722,10 +7720,10 @@
         <v>25016</v>
       </c>
       <c r="B383" s="90" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C383" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7733,10 +7731,10 @@
         <v>25017</v>
       </c>
       <c r="B384" s="90" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C384" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7744,10 +7742,10 @@
         <v>25028</v>
       </c>
       <c r="B385" s="90" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C385" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7755,10 +7753,10 @@
         <v>25032</v>
       </c>
       <c r="B386" s="90" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C386" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7766,10 +7764,10 @@
         <v>25041</v>
       </c>
       <c r="B387" s="90" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C387" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7777,10 +7775,10 @@
         <v>25046</v>
       </c>
       <c r="B388" s="90" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C388" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7788,10 +7786,10 @@
         <v>25060</v>
       </c>
       <c r="B389" s="90" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C389" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7799,10 +7797,10 @@
         <v>25064</v>
       </c>
       <c r="B390" s="90" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C390" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7810,10 +7808,10 @@
         <v>25066</v>
       </c>
       <c r="B391" s="90" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C391" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7821,10 +7819,10 @@
         <v>25067</v>
       </c>
       <c r="B392" s="90" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C392" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7832,10 +7830,10 @@
         <v>25071</v>
       </c>
       <c r="B393" s="90" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C393" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7843,10 +7841,10 @@
         <v>25081</v>
       </c>
       <c r="B394" s="90" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C394" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7854,10 +7852,10 @@
         <v>25084</v>
       </c>
       <c r="B395" s="90" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C395" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7865,10 +7863,10 @@
         <v>25088</v>
       </c>
       <c r="B396" s="90" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C396" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7876,10 +7874,10 @@
         <v>25094</v>
       </c>
       <c r="B397" s="90" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C397" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7887,10 +7885,10 @@
         <v>25099</v>
       </c>
       <c r="B398" s="90" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C398" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -7898,10 +7896,10 @@
         <v>25104</v>
       </c>
       <c r="B399" s="90" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C399" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -7909,10 +7907,10 @@
         <v>24120</v>
       </c>
       <c r="B400" s="147" t="s">
+        <v>422</v>
+      </c>
+      <c r="C400" s="92" t="s">
         <v>423</v>
-      </c>
-      <c r="C400" s="92" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -7920,10 +7918,10 @@
         <v>24125</v>
       </c>
       <c r="B401" s="148" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C401" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -7931,10 +7929,10 @@
         <v>24126</v>
       </c>
       <c r="B402" s="148" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C402" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -7942,10 +7940,10 @@
         <v>24128</v>
       </c>
       <c r="B403" s="148" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C403" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
@@ -7953,10 +7951,10 @@
         <v>24127</v>
       </c>
       <c r="B404" s="148" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C404" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -7964,10 +7962,10 @@
         <v>24131</v>
       </c>
       <c r="B405" s="148" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C405" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -7975,10 +7973,10 @@
         <v>24132</v>
       </c>
       <c r="B406" s="148" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C406" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -7986,10 +7984,10 @@
         <v>24121</v>
       </c>
       <c r="B407" s="148" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C407" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -7997,10 +7995,10 @@
         <v>24135</v>
       </c>
       <c r="B408" s="148" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C408" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -8008,10 +8006,10 @@
         <v>24136</v>
       </c>
       <c r="B409" s="148" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C409" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -8019,10 +8017,10 @@
         <v>24137</v>
       </c>
       <c r="B410" s="148" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C410" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -8030,10 +8028,10 @@
         <v>24139</v>
       </c>
       <c r="B411" s="148" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C411" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -8041,10 +8039,10 @@
         <v>24140</v>
       </c>
       <c r="B412" s="148" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C412" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -8052,10 +8050,10 @@
         <v>24141</v>
       </c>
       <c r="B413" s="148" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C413" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -8063,10 +8061,10 @@
         <v>24142</v>
       </c>
       <c r="B414" s="148" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C414" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -8074,10 +8072,10 @@
         <v>24145</v>
       </c>
       <c r="B415" s="148" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C415" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -8085,10 +8083,10 @@
         <v>24147</v>
       </c>
       <c r="B416" s="148" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C416" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -8096,10 +8094,10 @@
         <v>20023</v>
       </c>
       <c r="B417" s="149" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C417" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -8107,13 +8105,14 @@
         <v>24149</v>
       </c>
       <c r="B418" s="148" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C418" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C418" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8143,10 +8142,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8154,10 +8153,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>445</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8165,10 +8164,10 @@
         <v>10</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>447</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8176,10 +8175,10 @@
         <v>10</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>449</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8187,10 +8186,10 @@
         <v>10</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8198,10 +8197,10 @@
         <v>10</v>
       </c>
       <c r="B7" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>452</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8209,10 +8208,10 @@
         <v>10</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>454</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8220,10 +8219,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>456</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8231,10 +8230,10 @@
         <v>10</v>
       </c>
       <c r="B10" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>458</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8242,10 +8241,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>460</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8253,10 +8252,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8264,10 +8263,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>463</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8275,10 +8274,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>464</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>465</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8286,10 +8285,10 @@
         <v>38</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8297,10 +8296,10 @@
         <v>38</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8308,10 +8307,10 @@
         <v>38</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8319,10 +8318,10 @@
         <v>38</v>
       </c>
       <c r="B18" s="21" t="s">
+        <v>469</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>470</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8330,10 +8329,10 @@
         <v>38</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8341,10 +8340,10 @@
         <v>38</v>
       </c>
       <c r="B20" s="24" t="s">
+        <v>472</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>473</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8352,10 +8351,10 @@
         <v>38</v>
       </c>
       <c r="B21" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>475</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8363,10 +8362,10 @@
         <v>38</v>
       </c>
       <c r="B22" s="23" t="s">
+        <v>476</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>477</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8374,10 +8373,10 @@
         <v>38</v>
       </c>
       <c r="B23" s="26" t="s">
+        <v>478</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>479</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8385,10 +8384,10 @@
         <v>38</v>
       </c>
       <c r="B24" s="21" t="s">
+        <v>480</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>481</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8396,10 +8395,10 @@
         <v>38</v>
       </c>
       <c r="B25" s="23" t="s">
+        <v>482</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>483</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8407,10 +8406,10 @@
         <v>38</v>
       </c>
       <c r="B26" s="27" t="s">
+        <v>484</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>485</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8418,10 +8417,10 @@
         <v>38</v>
       </c>
       <c r="B27" s="21" t="s">
+        <v>486</v>
+      </c>
+      <c r="C27" s="22" t="s">
         <v>487</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8429,10 +8428,10 @@
         <v>38</v>
       </c>
       <c r="B28" s="23" t="s">
+        <v>488</v>
+      </c>
+      <c r="C28" s="14" t="s">
         <v>489</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8440,10 +8439,10 @@
         <v>38</v>
       </c>
       <c r="B29" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="C29" s="42" t="s">
         <v>491</v>
-      </c>
-      <c r="C29" s="42" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8451,10 +8450,10 @@
         <v>38</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8462,329 +8461,329 @@
         <v>38</v>
       </c>
       <c r="B31" s="39" t="s">
+        <v>493</v>
+      </c>
+      <c r="C31" s="42" t="s">
         <v>494</v>
-      </c>
-      <c r="C31" s="42" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B32" s="30" t="s">
+        <v>495</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>496</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C33" s="45" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C34" s="88" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B35" s="30" t="s">
+        <v>499</v>
+      </c>
+      <c r="C35" s="45" t="s">
         <v>500</v>
-      </c>
-      <c r="C35" s="45" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B37" s="26" t="s">
+        <v>502</v>
+      </c>
+      <c r="C37" s="32" t="s">
         <v>503</v>
-      </c>
-      <c r="C37" s="32" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B38" s="21" t="s">
+        <v>504</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>505</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C40" s="32" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B42" s="30" t="s">
+        <v>509</v>
+      </c>
+      <c r="C42" s="7" t="s">
         <v>510</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B43" s="30" t="s">
+        <v>511</v>
+      </c>
+      <c r="C43" s="7" t="s">
         <v>512</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B44" s="26" t="s">
+        <v>513</v>
+      </c>
+      <c r="C44" s="7" t="s">
         <v>514</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B45" s="72" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B46" s="63" t="s">
+        <v>515</v>
+      </c>
+      <c r="C46" s="14" t="s">
         <v>516</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B47" s="63" t="s">
+        <v>517</v>
+      </c>
+      <c r="C47" s="14" t="s">
         <v>518</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B48" s="44" t="s">
+        <v>519</v>
+      </c>
+      <c r="C48" s="14" t="s">
         <v>520</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B49" s="74" t="s">
+        <v>521</v>
+      </c>
+      <c r="C49" s="32" t="s">
         <v>522</v>
-      </c>
-      <c r="C49" s="32" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B51" s="30" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B52" s="31" t="s">
+        <v>525</v>
+      </c>
+      <c r="C52" s="19" t="s">
         <v>526</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B53" s="21" t="s">
+        <v>527</v>
+      </c>
+      <c r="C53" s="10" t="s">
         <v>528</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C54" s="84" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B55" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="C55" s="10" t="s">
         <v>531</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B56" s="64" t="s">
+        <v>532</v>
+      </c>
+      <c r="C56" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B57" s="30" t="s">
+        <v>534</v>
+      </c>
+      <c r="C57" s="54" t="s">
         <v>535</v>
-      </c>
-      <c r="C57" s="54" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B58" s="30" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C58" s="54" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B59" s="26" t="s">
+        <v>537</v>
+      </c>
+      <c r="C59" s="57" t="s">
         <v>538</v>
-      </c>
-      <c r="C59" s="57" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B60" s="21" t="s">
+        <v>539</v>
+      </c>
+      <c r="C60" s="76" t="s">
         <v>540</v>
-      </c>
-      <c r="C60" s="76" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8792,10 +8791,10 @@
         <v>73</v>
       </c>
       <c r="B61" s="23" t="s">
+        <v>541</v>
+      </c>
+      <c r="C61" s="78" t="s">
         <v>542</v>
-      </c>
-      <c r="C61" s="78" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8803,10 +8802,10 @@
         <v>73</v>
       </c>
       <c r="B62" s="24" t="s">
+        <v>543</v>
+      </c>
+      <c r="C62" s="54" t="s">
         <v>544</v>
-      </c>
-      <c r="C62" s="54" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8814,10 +8813,10 @@
         <v>73</v>
       </c>
       <c r="B63" s="21" t="s">
+        <v>545</v>
+      </c>
+      <c r="C63" s="56" t="s">
         <v>546</v>
-      </c>
-      <c r="C63" s="56" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8825,10 +8824,10 @@
         <v>73</v>
       </c>
       <c r="B64" s="29" t="s">
+        <v>547</v>
+      </c>
+      <c r="C64" s="75" t="s">
         <v>548</v>
-      </c>
-      <c r="C64" s="75" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8836,10 +8835,10 @@
         <v>73</v>
       </c>
       <c r="B65" s="40" t="s">
+        <v>549</v>
+      </c>
+      <c r="C65" s="55" t="s">
         <v>550</v>
-      </c>
-      <c r="C65" s="55" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8847,10 +8846,10 @@
         <v>73</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C66" s="55" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8858,10 +8857,10 @@
         <v>73</v>
       </c>
       <c r="B67" s="31" t="s">
+        <v>552</v>
+      </c>
+      <c r="C67" s="58" t="s">
         <v>553</v>
-      </c>
-      <c r="C67" s="58" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8869,10 +8868,10 @@
         <v>73</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8880,10 +8879,10 @@
         <v>73</v>
       </c>
       <c r="B69" s="24" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8891,10 +8890,10 @@
         <v>73</v>
       </c>
       <c r="B70" s="65" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8902,10 +8901,10 @@
         <v>73</v>
       </c>
       <c r="B71" s="25" t="s">
+        <v>495</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>496</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8913,10 +8912,10 @@
         <v>73</v>
       </c>
       <c r="B72" s="39" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8924,10 +8923,10 @@
         <v>73</v>
       </c>
       <c r="B73" s="24" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8935,10 +8934,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="43" t="s">
+        <v>499</v>
+      </c>
+      <c r="C74" s="77" t="s">
         <v>500</v>
-      </c>
-      <c r="C74" s="77" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8946,10 +8945,10 @@
         <v>73</v>
       </c>
       <c r="B75" s="44" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8957,10 +8956,10 @@
         <v>73</v>
       </c>
       <c r="B76" s="43" t="s">
+        <v>502</v>
+      </c>
+      <c r="C76" s="85" t="s">
         <v>503</v>
-      </c>
-      <c r="C76" s="85" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8968,10 +8967,10 @@
         <v>73</v>
       </c>
       <c r="B77" s="21" t="s">
+        <v>504</v>
+      </c>
+      <c r="C77" s="10" t="s">
         <v>505</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8979,10 +8978,10 @@
         <v>73</v>
       </c>
       <c r="B78" s="29" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8990,10 +8989,10 @@
         <v>73</v>
       </c>
       <c r="B79" s="73" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9001,10 +9000,10 @@
         <v>73</v>
       </c>
       <c r="B80" s="70" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9012,10 +9011,10 @@
         <v>73</v>
       </c>
       <c r="B81" s="48" t="s">
+        <v>509</v>
+      </c>
+      <c r="C81" s="79" t="s">
         <v>510</v>
-      </c>
-      <c r="C81" s="79" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9023,10 +9022,10 @@
         <v>73</v>
       </c>
       <c r="B82" s="48" t="s">
+        <v>511</v>
+      </c>
+      <c r="C82" s="79" t="s">
         <v>512</v>
-      </c>
-      <c r="C82" s="79" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9034,10 +9033,10 @@
         <v>73</v>
       </c>
       <c r="B83" s="49" t="s">
+        <v>513</v>
+      </c>
+      <c r="C83" s="79" t="s">
         <v>514</v>
-      </c>
-      <c r="C83" s="79" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9045,10 +9044,10 @@
         <v>73</v>
       </c>
       <c r="B84" s="48" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C84" s="46" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9056,2441 +9055,2441 @@
         <v>73</v>
       </c>
       <c r="B85" s="48" t="s">
+        <v>515</v>
+      </c>
+      <c r="C85" s="46" t="s">
         <v>516</v>
-      </c>
-      <c r="C85" s="46" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B86" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="C86" s="86" t="s">
         <v>558</v>
-      </c>
-      <c r="C86" s="86" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A87" s="53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B87" s="47" t="s">
+        <v>559</v>
+      </c>
+      <c r="C87" s="80" t="s">
         <v>560</v>
-      </c>
-      <c r="C87" s="80" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A88" s="53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B88" s="68" t="s">
         <v>8</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A89" s="53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B89" s="49" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C89" s="80" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A90" s="53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B90" s="47" t="s">
+        <v>563</v>
+      </c>
+      <c r="C90" s="51" t="s">
         <v>564</v>
-      </c>
-      <c r="C90" s="51" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A91" s="53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B91" s="66" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C91" s="52" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A92" s="61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B92" s="34" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C92" s="87" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="32.25" x14ac:dyDescent="0.3">
       <c r="A93" s="61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B93" s="69" t="s">
+        <v>567</v>
+      </c>
+      <c r="C93" s="83" t="s">
         <v>568</v>
-      </c>
-      <c r="C93" s="83" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A94" s="61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B94" s="69" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C94" s="82" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A95" s="61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B95" s="33" t="s">
+        <v>570</v>
+      </c>
+      <c r="C95" s="81" t="s">
         <v>571</v>
-      </c>
-      <c r="C95" s="81" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A96" s="61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B96" s="67" t="s">
+        <v>572</v>
+      </c>
+      <c r="C96" s="14" t="s">
         <v>573</v>
-      </c>
-      <c r="C96" s="14" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A97" s="61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B97" s="35" t="s">
+        <v>574</v>
+      </c>
+      <c r="C97" s="36" t="s">
         <v>575</v>
-      </c>
-      <c r="C97" s="36" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A98" s="61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B98" s="33" t="s">
+        <v>576</v>
+      </c>
+      <c r="C98" s="7" t="s">
         <v>577</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A99" s="61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B99" s="71" t="s">
+        <v>578</v>
+      </c>
+      <c r="C99" s="38" t="s">
         <v>579</v>
-      </c>
-      <c r="C99" s="38" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A100" s="61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B100" s="34" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C100" s="38" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="32.25" x14ac:dyDescent="0.3">
       <c r="A101" s="61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B101" s="35" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C101" s="38" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A102" s="61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B102" s="33" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C102" s="37" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A103" s="61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B103" s="34" t="s">
+        <v>583</v>
+      </c>
+      <c r="C103" s="38" t="s">
         <v>584</v>
-      </c>
-      <c r="C103" s="38" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A104" s="61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B104" s="34" t="s">
+        <v>585</v>
+      </c>
+      <c r="C104" s="38" t="s">
         <v>586</v>
-      </c>
-      <c r="C104" s="38" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A105" s="61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B105" s="35" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C105" s="32" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A106" s="61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B106" s="33" t="s">
+        <v>588</v>
+      </c>
+      <c r="C106" s="37" t="s">
         <v>589</v>
-      </c>
-      <c r="C106" s="37" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A107" s="61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B107" s="34" t="s">
+        <v>590</v>
+      </c>
+      <c r="C107" s="14" t="s">
         <v>591</v>
-      </c>
-      <c r="C107" s="14" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A108" s="61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B108" s="35" t="s">
+        <v>592</v>
+      </c>
+      <c r="C108" s="32" t="s">
         <v>593</v>
-      </c>
-      <c r="C108" s="32" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B109" t="s">
+        <v>594</v>
+      </c>
+      <c r="C109" t="s">
         <v>595</v>
-      </c>
-      <c r="C109" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B110" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C110" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B111" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C111" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B112" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C112" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B113" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C113" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B114" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C114" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B115" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C115" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B116" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C116" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B117" t="s">
+        <v>602</v>
+      </c>
+      <c r="C117" t="s">
         <v>603</v>
-      </c>
-      <c r="C117" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B118" t="s">
+        <v>604</v>
+      </c>
+      <c r="C118" t="s">
         <v>605</v>
-      </c>
-      <c r="C118" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B119" t="s">
+        <v>606</v>
+      </c>
+      <c r="C119" t="s">
         <v>607</v>
-      </c>
-      <c r="C119" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B120" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C120" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B121" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C121" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B122" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C122" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B123" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C123" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B124" t="s">
+        <v>592</v>
+      </c>
+      <c r="C124" t="s">
         <v>593</v>
-      </c>
-      <c r="C124" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B125" t="s">
+        <v>594</v>
+      </c>
+      <c r="C125" t="s">
         <v>595</v>
-      </c>
-      <c r="C125" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B126" t="s">
+        <v>610</v>
+      </c>
+      <c r="C126" t="s">
         <v>611</v>
-      </c>
-      <c r="C126" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B127" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C127" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B128" t="s">
+        <v>612</v>
+      </c>
+      <c r="C128" t="s">
         <v>613</v>
-      </c>
-      <c r="C128" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B129" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C129" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B130" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C130" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B131" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C131" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B132" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C132" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B133" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C133" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B134" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C134" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B135" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C135" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B136" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C136" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B137" t="s">
         <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B138" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C138" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B139" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C139" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B140" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C140" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B141" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C141" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B142" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C142" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B143" t="s">
+        <v>622</v>
+      </c>
+      <c r="C143" t="s">
         <v>623</v>
-      </c>
-      <c r="C143" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B144" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C144" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B145" t="s">
+        <v>625</v>
+      </c>
+      <c r="C145" t="s">
         <v>626</v>
-      </c>
-      <c r="C145" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B146" t="s">
         <v>5</v>
       </c>
       <c r="C146" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B147" t="s">
+        <v>627</v>
+      </c>
+      <c r="C147" t="s">
         <v>628</v>
-      </c>
-      <c r="C147" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B148" t="s">
+        <v>629</v>
+      </c>
+      <c r="C148" t="s">
         <v>630</v>
-      </c>
-      <c r="C148" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B149" t="s">
+        <v>631</v>
+      </c>
+      <c r="C149" t="s">
         <v>632</v>
-      </c>
-      <c r="C149" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B150" t="s">
+        <v>633</v>
+      </c>
+      <c r="C150" t="s">
         <v>634</v>
-      </c>
-      <c r="C150" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B151" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C151" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B152" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C152" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B153" t="s">
+        <v>637</v>
+      </c>
+      <c r="C153" t="s">
         <v>638</v>
-      </c>
-      <c r="C153" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B154" t="s">
+        <v>639</v>
+      </c>
+      <c r="C154" t="s">
         <v>640</v>
-      </c>
-      <c r="C154" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B155" t="s">
+        <v>641</v>
+      </c>
+      <c r="C155" t="s">
         <v>642</v>
-      </c>
-      <c r="C155" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B156" t="s">
+        <v>643</v>
+      </c>
+      <c r="C156" t="s">
         <v>644</v>
-      </c>
-      <c r="C156" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B157" t="s">
+        <v>645</v>
+      </c>
+      <c r="C157" t="s">
         <v>646</v>
-      </c>
-      <c r="C157" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B158" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C158" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B159" t="s">
+        <v>648</v>
+      </c>
+      <c r="C159" t="s">
         <v>649</v>
-      </c>
-      <c r="C159" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B160" t="s">
+        <v>650</v>
+      </c>
+      <c r="C160" t="s">
         <v>651</v>
-      </c>
-      <c r="C160" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B161" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C161" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B162" t="s">
+        <v>652</v>
+      </c>
+      <c r="C162" t="s">
         <v>653</v>
-      </c>
-      <c r="C162" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B163" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C163" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B164" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C164" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B165" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C165" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B166" t="s">
+        <v>657</v>
+      </c>
+      <c r="C166" t="s">
         <v>658</v>
-      </c>
-      <c r="C166" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B167" t="s">
+        <v>659</v>
+      </c>
+      <c r="C167" t="s">
         <v>660</v>
-      </c>
-      <c r="C167" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B168" t="s">
+        <v>661</v>
+      </c>
+      <c r="C168" t="s">
         <v>662</v>
-      </c>
-      <c r="C168" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B169" t="s">
+        <v>534</v>
+      </c>
+      <c r="C169" t="s">
         <v>535</v>
-      </c>
-      <c r="C169" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B170" t="s">
+        <v>663</v>
+      </c>
+      <c r="C170" t="s">
         <v>664</v>
-      </c>
-      <c r="C170" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B171" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C171" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B172" t="s">
+        <v>665</v>
+      </c>
+      <c r="C172" t="s">
         <v>666</v>
-      </c>
-      <c r="C172" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B173" t="s">
+        <v>667</v>
+      </c>
+      <c r="C173" t="s">
         <v>668</v>
-      </c>
-      <c r="C173" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B174" t="s">
+        <v>669</v>
+      </c>
+      <c r="C174" t="s">
         <v>670</v>
-      </c>
-      <c r="C174" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B175" t="s">
         <v>3</v>
       </c>
       <c r="C175" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B176" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C176" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B177" t="s">
+        <v>673</v>
+      </c>
+      <c r="C177" t="s">
         <v>674</v>
-      </c>
-      <c r="C177" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B178" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C178" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B179" t="s">
+        <v>675</v>
+      </c>
+      <c r="C179" t="s">
         <v>676</v>
-      </c>
-      <c r="C179" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B180" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C180" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B181" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C181" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B182" t="s">
+        <v>678</v>
+      </c>
+      <c r="C182" t="s">
         <v>679</v>
-      </c>
-      <c r="C182" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B183" t="s">
+        <v>680</v>
+      </c>
+      <c r="C183" t="s">
         <v>681</v>
-      </c>
-      <c r="C183" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B184" t="s">
+        <v>682</v>
+      </c>
+      <c r="C184" t="s">
         <v>683</v>
-      </c>
-      <c r="C184" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B185" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C185" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B186" t="s">
+        <v>685</v>
+      </c>
+      <c r="C186" t="s">
         <v>686</v>
-      </c>
-      <c r="C186" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B187" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C187" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B188" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C188" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B189" t="s">
+        <v>689</v>
+      </c>
+      <c r="C189" t="s">
         <v>690</v>
-      </c>
-      <c r="C189" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B190" t="s">
+        <v>691</v>
+      </c>
+      <c r="C190" t="s">
         <v>692</v>
-      </c>
-      <c r="C190" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B191" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C191" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B192" t="s">
+        <v>694</v>
+      </c>
+      <c r="C192" t="s">
         <v>695</v>
-      </c>
-      <c r="C192" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B193" t="s">
+        <v>696</v>
+      </c>
+      <c r="C193" t="s">
         <v>697</v>
-      </c>
-      <c r="C193" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B194" t="s">
+        <v>698</v>
+      </c>
+      <c r="C194" t="s">
         <v>699</v>
-      </c>
-      <c r="C194" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B195" t="s">
+        <v>700</v>
+      </c>
+      <c r="C195" t="s">
         <v>701</v>
-      </c>
-      <c r="C195" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B196" t="s">
+        <v>652</v>
+      </c>
+      <c r="C196" t="s">
         <v>653</v>
-      </c>
-      <c r="C196" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B197" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C197" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B198" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C198" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B199" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C199" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B200" t="s">
+        <v>657</v>
+      </c>
+      <c r="C200" t="s">
         <v>658</v>
-      </c>
-      <c r="C200" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B201" t="s">
+        <v>659</v>
+      </c>
+      <c r="C201" t="s">
         <v>660</v>
-      </c>
-      <c r="C201" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B202" t="s">
+        <v>661</v>
+      </c>
+      <c r="C202" t="s">
         <v>662</v>
-      </c>
-      <c r="C202" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B203" t="s">
+        <v>534</v>
+      </c>
+      <c r="C203" t="s">
         <v>535</v>
-      </c>
-      <c r="C203" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B204" t="s">
+        <v>663</v>
+      </c>
+      <c r="C204" t="s">
         <v>664</v>
-      </c>
-      <c r="C204" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B205" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C205" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B206" t="s">
+        <v>665</v>
+      </c>
+      <c r="C206" t="s">
         <v>666</v>
-      </c>
-      <c r="C206" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B207" t="s">
+        <v>667</v>
+      </c>
+      <c r="C207" t="s">
         <v>668</v>
-      </c>
-      <c r="C207" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B208" t="s">
+        <v>669</v>
+      </c>
+      <c r="C208" t="s">
         <v>670</v>
-      </c>
-      <c r="C208" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B209" t="s">
         <v>3</v>
       </c>
       <c r="C209" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B210" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C210" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B211" t="s">
+        <v>673</v>
+      </c>
+      <c r="C211" t="s">
         <v>674</v>
-      </c>
-      <c r="C211" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B212" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C212" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B213" t="s">
+        <v>702</v>
+      </c>
+      <c r="C213" t="s">
         <v>703</v>
-      </c>
-      <c r="C213" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B214" t="s">
+        <v>704</v>
+      </c>
+      <c r="C214" t="s">
         <v>705</v>
-      </c>
-      <c r="C214" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B215" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C215" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B216" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C216" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B217" t="s">
+        <v>708</v>
+      </c>
+      <c r="C217" t="s">
         <v>709</v>
-      </c>
-      <c r="C217" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B218" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C218" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B219" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C219" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B220" t="s">
+        <v>712</v>
+      </c>
+      <c r="C220" t="s">
         <v>713</v>
-      </c>
-      <c r="C220" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B221" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C221" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B222" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C222" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B223" t="s">
+        <v>716</v>
+      </c>
+      <c r="C223" t="s">
         <v>717</v>
-      </c>
-      <c r="C223" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B224" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C224" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B225" t="s">
+        <v>719</v>
+      </c>
+      <c r="C225" t="s">
         <v>720</v>
-      </c>
-      <c r="C225" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B226" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C226" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B227" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C227" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B228" t="s">
+        <v>723</v>
+      </c>
+      <c r="C228" t="s">
         <v>724</v>
-      </c>
-      <c r="C228" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B229" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C229" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B230" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C230" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B231" t="s">
+        <v>652</v>
+      </c>
+      <c r="C231" t="s">
         <v>653</v>
-      </c>
-      <c r="C231" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B232" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C232" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B233" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C233" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B234" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C234" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B235" t="s">
+        <v>657</v>
+      </c>
+      <c r="C235" t="s">
         <v>658</v>
-      </c>
-      <c r="C235" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B236" t="s">
+        <v>659</v>
+      </c>
+      <c r="C236" t="s">
         <v>660</v>
-      </c>
-      <c r="C236" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B237" t="s">
+        <v>661</v>
+      </c>
+      <c r="C237" t="s">
         <v>662</v>
-      </c>
-      <c r="C237" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B238" t="s">
+        <v>534</v>
+      </c>
+      <c r="C238" t="s">
         <v>535</v>
-      </c>
-      <c r="C238" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B239" t="s">
+        <v>663</v>
+      </c>
+      <c r="C239" t="s">
         <v>664</v>
-      </c>
-      <c r="C239" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B240" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C240" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B241" t="s">
+        <v>665</v>
+      </c>
+      <c r="C241" t="s">
         <v>666</v>
-      </c>
-      <c r="C241" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B242" t="s">
+        <v>667</v>
+      </c>
+      <c r="C242" t="s">
         <v>668</v>
-      </c>
-      <c r="C242" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B243" t="s">
+        <v>669</v>
+      </c>
+      <c r="C243" t="s">
         <v>670</v>
-      </c>
-      <c r="C243" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B244" t="s">
         <v>3</v>
       </c>
       <c r="C244" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B245" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C245" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B246" t="s">
+        <v>673</v>
+      </c>
+      <c r="C246" t="s">
         <v>674</v>
-      </c>
-      <c r="C246" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B247" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C247" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B248" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C248" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B249" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C249" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B250" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C250" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B251" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C251" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B252" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C252" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B253" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C253" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B254" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C254" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B255" t="s">
+        <v>543</v>
+      </c>
+      <c r="C255" t="s">
         <v>544</v>
-      </c>
-      <c r="C255" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B256" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C256" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B257" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C257" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B258" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C258" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B259" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C259" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B260" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C260" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B261" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C261" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B262" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C262" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B263" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C263" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B264" t="s">
+        <v>742</v>
+      </c>
+      <c r="C264" t="s">
         <v>743</v>
-      </c>
-      <c r="C264" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B265" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C265" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B266" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C266" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B267" t="s">
+        <v>746</v>
+      </c>
+      <c r="C267" t="s">
         <v>747</v>
-      </c>
-      <c r="C267" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B268" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C268" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B269" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C269" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B270" t="s">
+        <v>750</v>
+      </c>
+      <c r="C270" t="s">
         <v>751</v>
-      </c>
-      <c r="C270" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B271" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C271" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B272" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C272" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B273" t="s">
+        <v>753</v>
+      </c>
+      <c r="C273" t="s">
         <v>754</v>
-      </c>
-      <c r="C273" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B274" t="s">
+        <v>755</v>
+      </c>
+      <c r="C274" t="s">
         <v>756</v>
-      </c>
-      <c r="C274" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B275" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C275" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B276" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C276" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B277" t="s">
+        <v>746</v>
+      </c>
+      <c r="C277" t="s">
         <v>747</v>
-      </c>
-      <c r="C277" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B278" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C278" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B279" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C279" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B280" t="s">
+        <v>750</v>
+      </c>
+      <c r="C280" t="s">
         <v>751</v>
-      </c>
-      <c r="C280" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B281" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C281" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B282" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C282" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B283" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C283" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B284" t="s">
+        <v>755</v>
+      </c>
+      <c r="C284" t="s">
         <v>756</v>
-      </c>
-      <c r="C284" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B285" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C285" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B286" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C286" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B287" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C287" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B288" t="s">
+        <v>761</v>
+      </c>
+      <c r="C288" t="s">
         <v>762</v>
-      </c>
-      <c r="C288" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B289" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C289" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B290" t="s">
         <v>3</v>
       </c>
       <c r="C290" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B291" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C291" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B292" t="s">
+        <v>766</v>
+      </c>
+      <c r="C292" t="s">
         <v>767</v>
-      </c>
-      <c r="C292" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B293" t="s">
+        <v>768</v>
+      </c>
+      <c r="C293" t="s">
         <v>769</v>
-      </c>
-      <c r="C293" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B294" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C294" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B295" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C295" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B296" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C296" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B297" t="s">
+        <v>773</v>
+      </c>
+      <c r="C297" t="s">
         <v>774</v>
-      </c>
-      <c r="C297" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B298" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C298" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B299" t="s">
+        <v>482</v>
+      </c>
+      <c r="C299" t="s">
         <v>483</v>
-      </c>
-      <c r="C299" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B300" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C300" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B301" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C301" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B302" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C302" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B303" t="s">
+        <v>779</v>
+      </c>
+      <c r="C303" t="s">
         <v>780</v>
-      </c>
-      <c r="C303" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B304" t="s">
+        <v>480</v>
+      </c>
+      <c r="C304" t="s">
         <v>481</v>
-      </c>
-      <c r="C304" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B305" t="s">
+        <v>781</v>
+      </c>
+      <c r="C305" t="s">
         <v>782</v>
-      </c>
-      <c r="C305" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B306" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C306" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
   </sheetData>

--- a/Base.xlsx
+++ b/Base.xlsx
@@ -1,31 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LK\Desktop\GItHubUpload\EVALUATION-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Evaluation des ensignants\2025 2026\Application\ONLINE_VERSION_EVALUATION-2026\EVALUATION-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D874CBA-9689-4E86-AD68-72D55F392B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBAA62E-C585-4ED5-AF23-DADE221E5E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste" sheetId="3" r:id="rId1"/>
     <sheet name="Classification" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Classification!$A$1:$C$306</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Liste!$A$1:$C$418</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Classification!$A$1:$C$108</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="786">
   <si>
     <t>Classe</t>
   </si>
@@ -264,6 +268,9 @@
     <t>DJIKI Huguette</t>
   </si>
   <si>
+    <t>11TSS06</t>
+  </si>
+  <si>
     <t>DJITUPURI Emmanuel</t>
   </si>
   <si>
@@ -576,9 +583,6 @@
     <t xml:space="preserve">MAPANGUI MPABISSINA Jirson Yvanh </t>
   </si>
   <si>
-    <t>MBADOUM Egouyé</t>
-  </si>
-  <si>
     <t>EBOGO MENGUE Hugues</t>
   </si>
   <si>
@@ -2160,6 +2164,9 @@
     <t>Gestion des risques en finance</t>
   </si>
   <si>
+    <t>KAPNANG Brice Herman</t>
+  </si>
+  <si>
     <t>Modèles de courbes de taux</t>
   </si>
   <si>
@@ -2379,13 +2386,7 @@
     <t>Sport</t>
   </si>
   <si>
-    <t>AGBEDJINOU Léonard</t>
-  </si>
-  <si>
-    <t>NOUMEDEM Boris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCHUENTE </t>
+    <t xml:space="preserve">EGOUYE MBADOUM </t>
   </si>
 </sst>
 </file>
@@ -2531,6 +2532,7 @@
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2571,7 +2573,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -2797,41 +2799,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -2852,7 +2819,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3065,18 +3032,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3118,10 +3073,10 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="21" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="18" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3156,9 +3111,6 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3166,12 +3118,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3207,13 +3153,13 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="21" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="18" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="21" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3224,6 +3170,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3507,24 +3463,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C418"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F418"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="45" style="125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45" style="121" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="125" t="s">
+      <c r="B1" s="121" t="s">
         <v>6</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A2" s="89">
         <v>24010</v>
       </c>
@@ -3535,7 +3492,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A3" s="89">
         <v>25033</v>
       </c>
@@ -3546,7 +3503,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A4" s="89">
         <v>25013</v>
       </c>
@@ -3557,7 +3514,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A5" s="89">
         <v>25031</v>
       </c>
@@ -3568,7 +3525,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A6" s="89">
         <v>25004</v>
       </c>
@@ -3579,7 +3536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A7" s="89">
         <v>25019</v>
       </c>
@@ -3590,7 +3547,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A8" s="89">
         <v>25024</v>
       </c>
@@ -3601,7 +3558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A9" s="89">
         <v>25010</v>
       </c>
@@ -3612,7 +3569,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A10" s="89">
         <v>25012</v>
       </c>
@@ -3623,7 +3580,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A11" s="89">
         <v>25008</v>
       </c>
@@ -3634,7 +3591,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A12" s="89">
         <v>25030</v>
       </c>
@@ -3645,7 +3602,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A13" s="89">
         <v>25026</v>
       </c>
@@ -3656,7 +3613,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A14" s="89">
         <v>25022</v>
       </c>
@@ -3667,7 +3624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A15" s="89">
         <v>25023</v>
       </c>
@@ -3678,7 +3635,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A16" s="89">
         <v>25001</v>
       </c>
@@ -3689,7 +3646,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A17" s="89">
         <v>25020</v>
       </c>
@@ -3700,7 +3657,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A18" s="89">
         <v>25006</v>
       </c>
@@ -3711,7 +3668,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A19" s="89">
         <v>25009</v>
       </c>
@@ -3722,7 +3679,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A20" s="89">
         <v>25015</v>
       </c>
@@ -3733,7 +3690,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A21" s="89">
         <v>25025</v>
       </c>
@@ -3744,7 +3701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A22" s="89">
         <v>25021</v>
       </c>
@@ -3755,7 +3712,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A23" s="89">
         <v>25018</v>
       </c>
@@ -3766,7 +3723,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A24" s="89">
         <v>25003</v>
       </c>
@@ -3777,7 +3734,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A25" s="89">
         <v>24024</v>
       </c>
@@ -3788,7 +3745,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A26" s="89">
         <v>25027</v>
       </c>
@@ -3799,7 +3756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A27" s="89">
         <v>25014</v>
       </c>
@@ -3810,7 +3767,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A28" s="89">
         <v>25005</v>
       </c>
@@ -3821,18 +3778,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A29" s="91">
         <v>24002</v>
       </c>
-      <c r="B29" s="126" t="s">
+      <c r="B29" s="122" t="s">
         <v>37</v>
       </c>
       <c r="C29" s="92" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A30" s="89">
         <v>24003</v>
       </c>
@@ -3843,7 +3800,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A31" s="89">
         <v>24004</v>
       </c>
@@ -3854,7 +3811,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A32" s="89">
         <v>24005</v>
       </c>
@@ -3865,7 +3822,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A33" s="89">
         <v>24006</v>
       </c>
@@ -3876,7 +3833,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A34" s="89">
         <v>24007</v>
       </c>
@@ -3887,7 +3844,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A35" s="89">
         <v>24008</v>
       </c>
@@ -3898,7 +3855,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A36" s="89">
         <v>24009</v>
       </c>
@@ -3909,7 +3866,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A37" s="89">
         <v>24011</v>
       </c>
@@ -3920,7 +3877,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A38" s="89">
         <v>24012</v>
       </c>
@@ -3931,7 +3888,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A39" s="89">
         <v>24013</v>
       </c>
@@ -3942,7 +3899,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A40" s="89">
         <v>24014</v>
       </c>
@@ -3953,7 +3910,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A41" s="89">
         <v>24015</v>
       </c>
@@ -3964,7 +3921,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A42" s="89">
         <v>24016</v>
       </c>
@@ -3975,7 +3932,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A43" s="89">
         <v>24017</v>
       </c>
@@ -3986,7 +3943,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A44" s="89">
         <v>24018</v>
       </c>
@@ -3997,7 +3954,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A45" s="89">
         <v>24020</v>
       </c>
@@ -4008,7 +3965,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A46" s="89">
         <v>24022</v>
       </c>
@@ -4019,7 +3976,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A47" s="89">
         <v>24025</v>
       </c>
@@ -4030,7 +3987,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" ht="17" x14ac:dyDescent="0.45">
       <c r="A48" s="89">
         <v>24026</v>
       </c>
@@ -4041,7 +3998,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.45">
       <c r="A49" s="89">
         <v>24028</v>
       </c>
@@ -4052,7 +4009,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" ht="17" x14ac:dyDescent="0.45">
       <c r="A50" s="89">
         <v>24030</v>
       </c>
@@ -4063,7 +4020,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" ht="17" x14ac:dyDescent="0.45">
       <c r="A51" s="89">
         <v>24031</v>
       </c>
@@ -4074,7 +4031,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" ht="17" x14ac:dyDescent="0.45">
       <c r="A52" s="89">
         <v>24032</v>
       </c>
@@ -4085,7 +4042,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="17" x14ac:dyDescent="0.45">
       <c r="A53" s="89">
         <v>24033</v>
       </c>
@@ -4096,7 +4053,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.45">
       <c r="A54" s="89">
         <v>24035</v>
       </c>
@@ -4107,7 +4064,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" ht="17" x14ac:dyDescent="0.45">
       <c r="A55" s="89">
         <v>24036</v>
       </c>
@@ -4118,7 +4075,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" ht="17" x14ac:dyDescent="0.45">
       <c r="A56" s="89">
         <v>24037</v>
       </c>
@@ -4129,7 +4086,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" ht="17" x14ac:dyDescent="0.45">
       <c r="A57" s="89">
         <v>24038</v>
       </c>
@@ -4140,7 +4097,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" ht="17" x14ac:dyDescent="0.45">
       <c r="A58" s="89">
         <v>24040</v>
       </c>
@@ -4151,7 +4108,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.45">
       <c r="A59" s="89">
         <v>24042</v>
       </c>
@@ -4162,7 +4119,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" ht="17" x14ac:dyDescent="0.45">
       <c r="A60" s="89">
         <v>24043</v>
       </c>
@@ -4173,7 +4130,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" ht="17" x14ac:dyDescent="0.45">
       <c r="A61" s="89">
         <v>24044</v>
       </c>
@@ -4184,7 +4141,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" ht="17" x14ac:dyDescent="0.45">
       <c r="A62" s="89">
         <v>24045</v>
       </c>
@@ -4195,3506 +4152,3616 @@
         <v>38</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="94">
-        <v>23068</v>
-      </c>
-      <c r="B63" s="127" t="s">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="98">
+        <v>23069</v>
+      </c>
+      <c r="B63" s="92" t="s">
         <v>72</v>
       </c>
       <c r="C63" s="92" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="95">
-        <v>23069</v>
-      </c>
-      <c r="B64" s="125" t="s">
+      <c r="E63" s="143"/>
+      <c r="F63" s="144"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="99">
+        <v>23070</v>
+      </c>
+      <c r="B64" t="s">
         <v>74</v>
       </c>
       <c r="C64" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="95">
-        <v>23070</v>
-      </c>
-      <c r="B65" s="125" t="s">
+      <c r="E64" s="143"/>
+      <c r="F64" s="144"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="99">
+        <v>23071</v>
+      </c>
+      <c r="B65" t="s">
         <v>75</v>
       </c>
       <c r="C65" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="95">
-        <v>23071</v>
-      </c>
-      <c r="B66" s="125" t="s">
+      <c r="E65" s="143"/>
+      <c r="F65" s="144"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="99">
+        <v>23072</v>
+      </c>
+      <c r="B66" t="s">
         <v>76</v>
       </c>
       <c r="C66" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="95">
-        <v>23072</v>
-      </c>
-      <c r="B67" s="125" t="s">
+      <c r="E66" s="143"/>
+      <c r="F66" s="144"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="99">
+        <v>23073</v>
+      </c>
+      <c r="B67" t="s">
         <v>77</v>
       </c>
       <c r="C67" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="95">
-        <v>23073</v>
-      </c>
-      <c r="B68" s="125" t="s">
+      <c r="E67" s="143"/>
+      <c r="F67" s="144"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="99" t="s">
+        <v>79</v>
+      </c>
+      <c r="B68" t="s">
         <v>78</v>
       </c>
       <c r="C68" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="95">
-        <v>110006</v>
-      </c>
-      <c r="B69" s="125" t="s">
-        <v>79</v>
+      <c r="E68" s="143"/>
+      <c r="F68" s="144"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="99">
+        <v>25002</v>
+      </c>
+      <c r="B69" t="s">
+        <v>80</v>
       </c>
       <c r="C69" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="95">
-        <v>25002</v>
-      </c>
-      <c r="B70" s="125" t="s">
-        <v>80</v>
+      <c r="E69" s="143"/>
+      <c r="F69" s="144"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="99">
+        <v>23074</v>
+      </c>
+      <c r="B70" t="s">
+        <v>81</v>
       </c>
       <c r="C70" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="95">
-        <v>23074</v>
-      </c>
-      <c r="B71" s="125" t="s">
-        <v>81</v>
+      <c r="E70" s="143"/>
+      <c r="F70" s="144"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" s="99">
+        <v>23076</v>
+      </c>
+      <c r="B71" t="s">
+        <v>82</v>
       </c>
       <c r="C71" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="95">
-        <v>23075</v>
-      </c>
-      <c r="B72" s="125" t="s">
-        <v>82</v>
+      <c r="E71" s="143"/>
+      <c r="F71" s="144"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" s="99">
+        <v>23078</v>
+      </c>
+      <c r="B72" t="s">
+        <v>83</v>
       </c>
       <c r="C72" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="95">
-        <v>23076</v>
-      </c>
-      <c r="B73" s="125" t="s">
-        <v>83</v>
+      <c r="E72" s="143"/>
+      <c r="F72" s="144"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="99">
+        <v>23086</v>
+      </c>
+      <c r="B73" t="s">
+        <v>84</v>
       </c>
       <c r="C73" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="95">
-        <v>23078</v>
-      </c>
-      <c r="B74" s="125" t="s">
-        <v>84</v>
+      <c r="E73" s="143"/>
+      <c r="F73" s="144"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="99">
+        <v>23089</v>
+      </c>
+      <c r="B74" t="s">
+        <v>85</v>
       </c>
       <c r="C74" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="95">
-        <v>23079</v>
-      </c>
-      <c r="B75" s="125" t="s">
-        <v>85</v>
+      <c r="E74" s="143"/>
+      <c r="F74" s="144"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="99">
+        <v>14102</v>
+      </c>
+      <c r="B75" t="s">
+        <v>86</v>
       </c>
       <c r="C75" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="95">
-        <v>23080</v>
-      </c>
-      <c r="B76" s="125" t="s">
-        <v>86</v>
+      <c r="E75" s="143"/>
+      <c r="F75" s="144"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" s="99">
+        <v>23092</v>
+      </c>
+      <c r="B76" t="s">
+        <v>87</v>
       </c>
       <c r="C76" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="95">
-        <v>23081</v>
-      </c>
-      <c r="B77" s="125" t="s">
-        <v>87</v>
+      <c r="E76" s="143"/>
+      <c r="F76" s="144"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="99">
+        <v>23093</v>
+      </c>
+      <c r="B77" t="s">
+        <v>88</v>
       </c>
       <c r="C77" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="95">
-        <v>23082</v>
-      </c>
-      <c r="B78" s="125" t="s">
-        <v>88</v>
+      <c r="E77" s="143"/>
+      <c r="F77" s="144"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" s="99">
+        <v>23096</v>
+      </c>
+      <c r="B78" t="s">
+        <v>89</v>
       </c>
       <c r="C78" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="95">
-        <v>23083</v>
-      </c>
-      <c r="B79" s="125" t="s">
-        <v>89</v>
+      <c r="E78" s="143"/>
+      <c r="F78" s="144"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" s="99">
+        <v>22062</v>
+      </c>
+      <c r="B79" t="s">
+        <v>90</v>
       </c>
       <c r="C79" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="95">
-        <v>23086</v>
-      </c>
-      <c r="B80" s="125" t="s">
-        <v>90</v>
+      <c r="E79" s="143"/>
+      <c r="F79" s="144"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="99">
+        <v>23099</v>
+      </c>
+      <c r="B80" t="s">
+        <v>91</v>
       </c>
       <c r="C80" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="96">
-        <v>23087</v>
-      </c>
-      <c r="B81" s="125" t="s">
-        <v>91</v>
+      <c r="E80" s="143"/>
+      <c r="F80" s="144"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" s="99">
+        <v>23101</v>
+      </c>
+      <c r="B81" t="s">
+        <v>92</v>
       </c>
       <c r="C81" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="97">
+      <c r="E81" s="143"/>
+      <c r="F81" s="144"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="98">
+        <v>23068</v>
+      </c>
+      <c r="B82" s="92" t="s">
+        <v>93</v>
+      </c>
+      <c r="C82" s="92" t="s">
+        <v>94</v>
+      </c>
+      <c r="E82" s="143"/>
+      <c r="F82" s="144"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="99">
+        <v>23075</v>
+      </c>
+      <c r="B83" t="s">
+        <v>95</v>
+      </c>
+      <c r="C83" t="s">
+        <v>94</v>
+      </c>
+      <c r="E83" s="143"/>
+      <c r="F83" s="144"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" s="99">
+        <v>23079</v>
+      </c>
+      <c r="B84" t="s">
+        <v>96</v>
+      </c>
+      <c r="C84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E84" s="143"/>
+      <c r="F84" s="144"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="99">
+        <v>23080</v>
+      </c>
+      <c r="B85" t="s">
+        <v>97</v>
+      </c>
+      <c r="C85" t="s">
+        <v>94</v>
+      </c>
+      <c r="E85" s="143"/>
+      <c r="F85" s="144"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="99">
+        <v>23081</v>
+      </c>
+      <c r="B86" t="s">
+        <v>98</v>
+      </c>
+      <c r="C86" t="s">
+        <v>94</v>
+      </c>
+      <c r="E86" s="143"/>
+      <c r="F86" s="144"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="99">
+        <v>23082</v>
+      </c>
+      <c r="B87" t="s">
+        <v>99</v>
+      </c>
+      <c r="C87" t="s">
+        <v>94</v>
+      </c>
+      <c r="E87" s="143"/>
+      <c r="F87" s="144"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="99">
+        <v>23083</v>
+      </c>
+      <c r="B88" t="s">
+        <v>100</v>
+      </c>
+      <c r="C88" t="s">
+        <v>94</v>
+      </c>
+      <c r="E88" s="143"/>
+      <c r="F88" s="144"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="99">
+        <v>23087</v>
+      </c>
+      <c r="B89" t="s">
+        <v>101</v>
+      </c>
+      <c r="C89" t="s">
+        <v>94</v>
+      </c>
+      <c r="E89" s="143"/>
+      <c r="F89" s="144"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="99">
         <v>23088</v>
       </c>
-      <c r="B82" s="127" t="s">
-        <v>92</v>
-      </c>
-      <c r="C82" s="92" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="95">
-        <v>23089</v>
-      </c>
-      <c r="B83" s="125" t="s">
+      <c r="B90" t="s">
+        <v>102</v>
+      </c>
+      <c r="C90" t="s">
         <v>94</v>
       </c>
-      <c r="C83" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="95">
+      <c r="E90" s="143"/>
+      <c r="F90" s="144"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="99">
         <v>23090</v>
       </c>
-      <c r="B84" s="125" t="s">
-        <v>95</v>
-      </c>
-      <c r="C84" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="95">
-        <v>14102</v>
-      </c>
-      <c r="B85" s="125" t="s">
-        <v>96</v>
-      </c>
-      <c r="C85" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="98">
+      <c r="B91" t="s">
+        <v>103</v>
+      </c>
+      <c r="C91" t="s">
+        <v>94</v>
+      </c>
+      <c r="E91" s="143"/>
+      <c r="F91" s="144"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="94">
         <v>23091</v>
       </c>
-      <c r="B86" s="125" t="s">
-        <v>97</v>
-      </c>
-      <c r="C86" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="95">
-        <v>23092</v>
-      </c>
-      <c r="B87" s="125" t="s">
-        <v>98</v>
-      </c>
-      <c r="C87" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="95">
+      <c r="B92" t="s">
+        <v>104</v>
+      </c>
+      <c r="C92" t="s">
+        <v>94</v>
+      </c>
+      <c r="E92" s="143"/>
+      <c r="F92" s="144"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="99">
         <v>25082</v>
       </c>
-      <c r="B88" s="125" t="s">
-        <v>99</v>
-      </c>
-      <c r="C88" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="95">
-        <v>23093</v>
-      </c>
-      <c r="B89" s="125" t="s">
-        <v>100</v>
-      </c>
-      <c r="C89" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="95">
+      <c r="B93" t="s">
+        <v>105</v>
+      </c>
+      <c r="C93" t="s">
+        <v>94</v>
+      </c>
+      <c r="E93" s="143"/>
+      <c r="F93" s="144"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="99">
         <v>23095</v>
       </c>
-      <c r="B90" s="125" t="s">
-        <v>101</v>
-      </c>
-      <c r="C90" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="95">
-        <v>23096</v>
-      </c>
-      <c r="B91" s="125" t="s">
-        <v>102</v>
-      </c>
-      <c r="C91" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="95">
-        <v>22062</v>
-      </c>
-      <c r="B92" s="125" t="s">
-        <v>103</v>
-      </c>
-      <c r="C92" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="95">
-        <v>23099</v>
-      </c>
-      <c r="B93" s="125" t="s">
-        <v>104</v>
-      </c>
-      <c r="C93" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="95">
-        <v>23101</v>
-      </c>
-      <c r="B94" s="125" t="s">
-        <v>105</v>
+      <c r="B94" t="s">
+        <v>106</v>
       </c>
       <c r="C94" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A95" s="99">
+        <v>94</v>
+      </c>
+      <c r="E94" s="143"/>
+      <c r="F94" s="144"/>
+    </row>
+    <row r="95" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A95" s="95">
         <v>25040</v>
       </c>
-      <c r="B95" s="128" t="s">
-        <v>106</v>
+      <c r="B95" s="123" t="s">
+        <v>107</v>
       </c>
       <c r="C95" s="92" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A96" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A96" s="96">
         <v>24046</v>
       </c>
-      <c r="B96" s="129" t="s">
+      <c r="B96" s="124" t="s">
+        <v>109</v>
+      </c>
+      <c r="C96" t="s">
         <v>108</v>
       </c>
-      <c r="C96" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A97" s="100">
+    </row>
+    <row r="97" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A97" s="96">
         <v>25042</v>
       </c>
-      <c r="B97" s="129" t="s">
-        <v>109</v>
+      <c r="B97" s="124" t="s">
+        <v>110</v>
       </c>
       <c r="C97" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A98" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A98" s="96">
         <v>25043</v>
       </c>
-      <c r="B98" s="129" t="s">
-        <v>110</v>
+      <c r="B98" s="124" t="s">
+        <v>111</v>
       </c>
       <c r="C98" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A99" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A99" s="96">
         <v>25044</v>
       </c>
-      <c r="B99" s="129" t="s">
-        <v>111</v>
+      <c r="B99" s="124" t="s">
+        <v>112</v>
       </c>
       <c r="C99" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A100" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A100" s="96">
         <v>24124</v>
       </c>
-      <c r="B100" s="129" t="s">
-        <v>112</v>
+      <c r="B100" s="124" t="s">
+        <v>113</v>
       </c>
       <c r="C100" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A101" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A101" s="96">
         <v>25045</v>
       </c>
-      <c r="B101" s="129" t="s">
-        <v>113</v>
+      <c r="B101" s="124" t="s">
+        <v>114</v>
       </c>
       <c r="C101" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A102" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A102" s="96">
         <v>25047</v>
       </c>
-      <c r="B102" s="129" t="s">
-        <v>114</v>
+      <c r="B102" s="124" t="s">
+        <v>115</v>
       </c>
       <c r="C102" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A103" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A103" s="96">
         <v>25048</v>
       </c>
-      <c r="B103" s="129" t="s">
-        <v>115</v>
+      <c r="B103" s="124" t="s">
+        <v>116</v>
       </c>
       <c r="C103" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A104" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A104" s="96">
         <v>25049</v>
       </c>
-      <c r="B104" s="129" t="s">
-        <v>116</v>
+      <c r="B104" s="124" t="s">
+        <v>117</v>
       </c>
       <c r="C104" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A105" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A105" s="96">
         <v>25050</v>
       </c>
-      <c r="B105" s="129" t="s">
-        <v>117</v>
+      <c r="B105" s="124" t="s">
+        <v>118</v>
       </c>
       <c r="C105" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A106" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A106" s="96">
         <v>25051</v>
       </c>
-      <c r="B106" s="129" t="s">
-        <v>118</v>
+      <c r="B106" s="124" t="s">
+        <v>119</v>
       </c>
       <c r="C106" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A107" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A107" s="96">
         <v>25052</v>
       </c>
-      <c r="B107" s="129" t="s">
-        <v>119</v>
+      <c r="B107" s="124" t="s">
+        <v>120</v>
       </c>
       <c r="C107" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A108" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A108" s="96">
         <v>25053</v>
       </c>
-      <c r="B108" s="129" t="s">
-        <v>120</v>
+      <c r="B108" s="124" t="s">
+        <v>121</v>
       </c>
       <c r="C108" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A109" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A109" s="96">
         <v>25054</v>
       </c>
-      <c r="B109" s="129" t="s">
-        <v>121</v>
+      <c r="B109" s="124" t="s">
+        <v>122</v>
       </c>
       <c r="C109" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A110" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A110" s="96">
         <v>25055</v>
       </c>
-      <c r="B110" s="129" t="s">
-        <v>122</v>
+      <c r="B110" s="124" t="s">
+        <v>123</v>
       </c>
       <c r="C110" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A111" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A111" s="96">
         <v>25056</v>
       </c>
-      <c r="B111" s="129" t="s">
-        <v>123</v>
+      <c r="B111" s="124" t="s">
+        <v>124</v>
       </c>
       <c r="C111" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A112" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A112" s="96">
         <v>25057</v>
       </c>
-      <c r="B112" s="129" t="s">
-        <v>124</v>
+      <c r="B112" s="124" t="s">
+        <v>125</v>
       </c>
       <c r="C112" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A113" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A113" s="96">
         <v>25058</v>
       </c>
-      <c r="B113" s="129" t="s">
-        <v>125</v>
+      <c r="B113" s="124" t="s">
+        <v>126</v>
       </c>
       <c r="C113" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A114" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A114" s="96">
         <v>25059</v>
       </c>
-      <c r="B114" s="129" t="s">
-        <v>126</v>
+      <c r="B114" s="124" t="s">
+        <v>127</v>
       </c>
       <c r="C114" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A115" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A115" s="96">
         <v>25061</v>
       </c>
-      <c r="B115" s="129" t="s">
-        <v>127</v>
+      <c r="B115" s="124" t="s">
+        <v>128</v>
       </c>
       <c r="C115" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A116" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A116" s="96">
         <v>25062</v>
       </c>
-      <c r="B116" s="129" t="s">
-        <v>128</v>
+      <c r="B116" s="124" t="s">
+        <v>129</v>
       </c>
       <c r="C116" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A117" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A117" s="96">
         <v>25063</v>
       </c>
-      <c r="B117" s="129" t="s">
-        <v>129</v>
+      <c r="B117" s="124" t="s">
+        <v>130</v>
       </c>
       <c r="C117" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A118" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A118" s="96">
         <v>25065</v>
       </c>
-      <c r="B118" s="129" t="s">
-        <v>130</v>
+      <c r="B118" s="124" t="s">
+        <v>131</v>
       </c>
       <c r="C118" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A119" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A119" s="96">
         <v>25068</v>
       </c>
-      <c r="B119" s="129" t="s">
-        <v>131</v>
+      <c r="B119" s="124" t="s">
+        <v>132</v>
       </c>
       <c r="C119" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A120" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A120" s="96">
         <v>25069</v>
       </c>
-      <c r="B120" s="129" t="s">
-        <v>132</v>
+      <c r="B120" s="124" t="s">
+        <v>133</v>
       </c>
       <c r="C120" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A121" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A121" s="96">
         <v>25070</v>
       </c>
-      <c r="B121" s="129" t="s">
-        <v>133</v>
+      <c r="B121" s="124" t="s">
+        <v>134</v>
       </c>
       <c r="C121" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A122" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A122" s="96">
         <v>25072</v>
       </c>
-      <c r="B122" s="130" t="s">
-        <v>134</v>
+      <c r="B122" s="125" t="s">
+        <v>135</v>
       </c>
       <c r="C122" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A123" s="100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A123" s="96">
         <v>25073</v>
       </c>
-      <c r="B123" s="130" t="s">
-        <v>135</v>
+      <c r="B123" s="125" t="s">
+        <v>136</v>
       </c>
       <c r="C123" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A124" s="101">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A124" s="97">
         <v>24047</v>
       </c>
-      <c r="B124" s="126" t="s">
-        <v>136</v>
+      <c r="B124" s="122" t="s">
+        <v>137</v>
       </c>
       <c r="C124" s="92" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A125" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A125" s="94">
         <v>24048</v>
       </c>
       <c r="B125" s="90" t="s">
+        <v>139</v>
+      </c>
+      <c r="C125" t="s">
         <v>138</v>
       </c>
-      <c r="C125" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A126" s="98">
+    </row>
+    <row r="126" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A126" s="94">
         <v>24050</v>
       </c>
       <c r="B126" s="90" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C126" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A127" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A127" s="94">
         <v>24051</v>
       </c>
       <c r="B127" s="90" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C127" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A128" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A128" s="94">
         <v>24052</v>
       </c>
       <c r="B128" s="90" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C128" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A129" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A129" s="94">
         <v>24053</v>
       </c>
       <c r="B129" s="90" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C129" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A130" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A130" s="94">
         <v>24055</v>
       </c>
       <c r="B130" s="90" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C130" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A131" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A131" s="94">
         <v>24056</v>
       </c>
       <c r="B131" s="90" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C131" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A132" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A132" s="94">
         <v>24057</v>
       </c>
       <c r="B132" s="90" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C132" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A133" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A133" s="94">
         <v>24058</v>
       </c>
       <c r="B133" s="90" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C133" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A134" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A134" s="94">
         <v>24059</v>
       </c>
       <c r="B134" s="90" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C134" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A135" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A135" s="94">
         <v>24060</v>
       </c>
       <c r="B135" s="90" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C135" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A136" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A136" s="94">
         <v>24061</v>
       </c>
       <c r="B136" s="90" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C136" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A137" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A137" s="94">
         <v>24062</v>
       </c>
       <c r="B137" s="90" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C137" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A138" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A138" s="94">
         <v>24063</v>
       </c>
       <c r="B138" s="90" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C138" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A139" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A139" s="94">
         <v>24064</v>
       </c>
       <c r="B139" s="90" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C139" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A140" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A140" s="94">
         <v>24065</v>
       </c>
       <c r="B140" s="90" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C140" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A141" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A141" s="94">
         <v>24066</v>
       </c>
       <c r="B141" s="90" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C141" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A142" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A142" s="94">
         <v>23050</v>
       </c>
       <c r="B142" s="90" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C142" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A143" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A143" s="94">
         <v>24067</v>
       </c>
       <c r="B143" s="90" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C143" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A144" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A144" s="94">
         <v>24068</v>
       </c>
       <c r="B144" s="90" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C144" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A145" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="17" x14ac:dyDescent="0.45">
+      <c r="A145" s="94">
         <v>24069</v>
       </c>
       <c r="B145" s="90" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C145" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A146" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="17" x14ac:dyDescent="0.45">
+      <c r="A146" s="94">
         <v>24070</v>
       </c>
       <c r="B146" s="90" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C146" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A147" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" ht="17" x14ac:dyDescent="0.45">
+      <c r="A147" s="94">
         <v>23058</v>
       </c>
       <c r="B147" s="90" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C147" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A148" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="17" x14ac:dyDescent="0.45">
+      <c r="A148" s="94">
         <v>24071</v>
       </c>
       <c r="B148" s="90" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C148" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A149" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="17" x14ac:dyDescent="0.45">
+      <c r="A149" s="94">
         <v>24072</v>
       </c>
       <c r="B149" s="90" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C149" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A150" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="17" x14ac:dyDescent="0.45">
+      <c r="A150" s="94">
         <v>24073</v>
       </c>
       <c r="B150" s="90" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C150" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A151" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="17" x14ac:dyDescent="0.45">
+      <c r="A151" s="94">
         <v>24074</v>
       </c>
       <c r="B151" s="90" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C151" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A152" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="17" x14ac:dyDescent="0.45">
+      <c r="A152" s="94">
         <v>24075</v>
       </c>
       <c r="B152" s="90" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C152" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A153" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="17" x14ac:dyDescent="0.45">
+      <c r="A153" s="94">
         <v>24076</v>
       </c>
       <c r="B153" s="90" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C153" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A154" s="98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" ht="17" x14ac:dyDescent="0.45">
+      <c r="A154" s="94">
         <v>24079</v>
       </c>
       <c r="B154" s="90" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C154" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A155" s="102">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A155" s="98">
         <v>23039</v>
       </c>
-      <c r="B155" s="131" t="s">
-        <v>168</v>
+      <c r="B155" s="146" t="s">
+        <v>169</v>
       </c>
       <c r="C155" s="92" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A156" s="103">
+        <v>170</v>
+      </c>
+      <c r="E155" s="143"/>
+      <c r="F155" s="147"/>
+    </row>
+    <row r="156" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A156" s="99">
         <v>23040</v>
       </c>
-      <c r="B156" s="132" t="s">
+      <c r="B156" s="145" t="s">
+        <v>171</v>
+      </c>
+      <c r="C156" t="s">
         <v>170</v>
       </c>
-      <c r="C156" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A157" s="103">
+      <c r="E156" s="143"/>
+      <c r="F156" s="147"/>
+    </row>
+    <row r="157" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A157" s="99">
         <v>23041</v>
       </c>
-      <c r="B157" s="132" t="s">
-        <v>171</v>
+      <c r="B157" s="145" t="s">
+        <v>172</v>
       </c>
       <c r="C157" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A158" s="103">
+        <v>170</v>
+      </c>
+      <c r="E157" s="143"/>
+      <c r="F157" s="147"/>
+    </row>
+    <row r="158" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A158" s="99">
         <v>23042</v>
       </c>
-      <c r="B158" s="132" t="s">
-        <v>172</v>
+      <c r="B158" s="145" t="s">
+        <v>173</v>
       </c>
       <c r="C158" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A159" s="103">
+        <v>170</v>
+      </c>
+      <c r="E158" s="143"/>
+      <c r="F158" s="147"/>
+    </row>
+    <row r="159" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A159" s="99">
         <v>23043</v>
       </c>
-      <c r="B159" s="132" t="s">
-        <v>173</v>
+      <c r="B159" s="145" t="s">
+        <v>174</v>
       </c>
       <c r="C159" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A160" s="103">
+        <v>170</v>
+      </c>
+      <c r="E159" s="143"/>
+      <c r="F159" s="147"/>
+    </row>
+    <row r="160" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A160" s="99">
         <v>23044</v>
       </c>
-      <c r="B160" s="132" t="s">
-        <v>174</v>
+      <c r="B160" s="145" t="s">
+        <v>175</v>
       </c>
       <c r="C160" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A161" s="103">
+        <v>170</v>
+      </c>
+      <c r="E160" s="143"/>
+      <c r="F160" s="147"/>
+    </row>
+    <row r="161" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A161" s="99">
         <v>23045</v>
       </c>
-      <c r="B161" s="132" t="s">
-        <v>175</v>
+      <c r="B161" s="145" t="s">
+        <v>176</v>
       </c>
       <c r="C161" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A162" s="104">
+        <v>170</v>
+      </c>
+      <c r="E161" s="143"/>
+      <c r="F161" s="147"/>
+    </row>
+    <row r="162" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A162" s="100">
         <v>22073</v>
       </c>
-      <c r="B162" s="132" t="s">
-        <v>176</v>
+      <c r="B162" s="145" t="s">
+        <v>184</v>
       </c>
       <c r="C162" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A163" s="103">
+        <v>170</v>
+      </c>
+      <c r="E162" s="148"/>
+      <c r="F162" s="147"/>
+    </row>
+    <row r="163" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A163" s="99">
         <v>23057</v>
       </c>
-      <c r="B163" s="132" t="s">
+      <c r="B163" s="145" t="s">
+        <v>785</v>
+      </c>
+      <c r="C163" t="s">
+        <v>170</v>
+      </c>
+      <c r="E163" s="143"/>
+      <c r="F163" s="147"/>
+    </row>
+    <row r="164" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A164" s="99">
+        <v>23046</v>
+      </c>
+      <c r="B164" s="145" t="s">
         <v>177</v>
       </c>
-      <c r="C163" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A164" s="103">
-        <v>23046</v>
-      </c>
-      <c r="B164" s="132" t="s">
+      <c r="C164" t="s">
+        <v>170</v>
+      </c>
+      <c r="E164" s="143"/>
+      <c r="F164" s="147"/>
+    </row>
+    <row r="165" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A165" s="99">
+        <v>23047</v>
+      </c>
+      <c r="B165" s="145" t="s">
         <v>178</v>
       </c>
-      <c r="C164" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A165" s="103">
-        <v>23047</v>
-      </c>
-      <c r="B165" s="132" t="s">
+      <c r="C165" t="s">
+        <v>170</v>
+      </c>
+      <c r="E165" s="143"/>
+      <c r="F165" s="147"/>
+    </row>
+    <row r="166" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A166" s="99">
+        <v>23049</v>
+      </c>
+      <c r="B166" s="145" t="s">
         <v>179</v>
       </c>
-      <c r="C165" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A166" s="103">
-        <v>23049</v>
-      </c>
-      <c r="B166" s="132" t="s">
+      <c r="C166" t="s">
+        <v>170</v>
+      </c>
+      <c r="E166" s="143"/>
+      <c r="F166" s="147"/>
+    </row>
+    <row r="167" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A167" s="99">
+        <v>23051</v>
+      </c>
+      <c r="B167" s="145" t="s">
         <v>180</v>
       </c>
-      <c r="C166" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A167" s="103">
-        <v>23051</v>
-      </c>
-      <c r="B167" s="132" t="s">
+      <c r="C167" t="s">
+        <v>170</v>
+      </c>
+      <c r="E167" s="143"/>
+      <c r="F167" s="147"/>
+    </row>
+    <row r="168" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A168" s="99">
+        <v>23053</v>
+      </c>
+      <c r="B168" s="145" t="s">
         <v>181</v>
       </c>
-      <c r="C167" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A168" s="103">
-        <v>23053</v>
-      </c>
-      <c r="B168" s="132" t="s">
+      <c r="C168" t="s">
+        <v>170</v>
+      </c>
+      <c r="E168" s="143"/>
+      <c r="F168" s="147"/>
+    </row>
+    <row r="169" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A169" s="99">
+        <v>23055</v>
+      </c>
+      <c r="B169" s="145" t="s">
         <v>182</v>
       </c>
-      <c r="C168" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A169" s="103">
-        <v>23055</v>
-      </c>
-      <c r="B169" s="132" t="s">
+      <c r="C169" t="s">
+        <v>170</v>
+      </c>
+      <c r="E169" s="143"/>
+      <c r="F169" s="147"/>
+    </row>
+    <row r="170" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A170" s="99">
+        <v>23056</v>
+      </c>
+      <c r="B170" s="145" t="s">
         <v>183</v>
       </c>
-      <c r="C169" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A170" s="103">
-        <v>23056</v>
-      </c>
-      <c r="B170" s="132" t="s">
-        <v>184</v>
-      </c>
       <c r="C170" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A171" s="103">
+        <v>170</v>
+      </c>
+      <c r="E170" s="143"/>
+      <c r="F170" s="147"/>
+    </row>
+    <row r="171" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A171" s="99">
         <v>23059</v>
       </c>
-      <c r="B171" s="132" t="s">
+      <c r="B171" s="145" t="s">
         <v>185</v>
       </c>
       <c r="C171" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A172" s="103">
+        <v>170</v>
+      </c>
+      <c r="E171" s="143"/>
+      <c r="F171" s="147"/>
+    </row>
+    <row r="172" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A172" s="99">
         <v>23060</v>
       </c>
-      <c r="B172" s="132" t="s">
+      <c r="B172" s="145" t="s">
         <v>186</v>
       </c>
       <c r="C172" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A173" s="103">
+        <v>170</v>
+      </c>
+      <c r="E172" s="143"/>
+      <c r="F172" s="147"/>
+    </row>
+    <row r="173" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A173" s="99">
         <v>23062</v>
       </c>
-      <c r="B173" s="132" t="s">
+      <c r="B173" s="145" t="s">
         <v>187</v>
       </c>
       <c r="C173" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A174" s="103">
+        <v>170</v>
+      </c>
+      <c r="E173" s="143"/>
+      <c r="F173" s="147"/>
+    </row>
+    <row r="174" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A174" s="99">
         <v>23063</v>
       </c>
-      <c r="B174" s="132" t="s">
+      <c r="B174" s="145" t="s">
         <v>188</v>
       </c>
       <c r="C174" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A175" s="103">
+        <v>170</v>
+      </c>
+      <c r="E174" s="143"/>
+      <c r="F174" s="147"/>
+    </row>
+    <row r="175" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A175" s="99">
         <v>23064</v>
       </c>
-      <c r="B175" s="132" t="s">
+      <c r="B175" s="145" t="s">
         <v>189</v>
       </c>
       <c r="C175" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A176" s="103">
+        <v>170</v>
+      </c>
+      <c r="E175" s="143"/>
+      <c r="F175" s="147"/>
+    </row>
+    <row r="176" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A176" s="99">
         <v>23065</v>
       </c>
-      <c r="B176" s="132" t="s">
+      <c r="B176" s="145" t="s">
         <v>190</v>
       </c>
       <c r="C176" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A177" s="103">
+        <v>170</v>
+      </c>
+      <c r="E176" s="143"/>
+      <c r="F176" s="147"/>
+    </row>
+    <row r="177" spans="1:6" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A177" s="99">
         <v>23067</v>
       </c>
-      <c r="B177" s="132" t="s">
+      <c r="B177" s="145" t="s">
         <v>191</v>
       </c>
       <c r="C177" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="105">
+        <v>170</v>
+      </c>
+      <c r="E177" s="143"/>
+      <c r="F177" s="147"/>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A178" s="101">
         <v>24094</v>
       </c>
-      <c r="B178" s="133" t="s">
+      <c r="B178" s="126" t="s">
         <v>192</v>
       </c>
       <c r="C178" s="92" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="106">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A179" s="102">
         <v>22067</v>
       </c>
-      <c r="B179" s="134" t="s">
+      <c r="B179" s="127" t="s">
         <v>194</v>
       </c>
       <c r="C179" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="107">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A180" s="103">
         <v>21001</v>
       </c>
-      <c r="B180" s="135" t="s">
+      <c r="B180" s="128" t="s">
         <v>195</v>
       </c>
       <c r="C180" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="107">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A181" s="103">
         <v>18093</v>
       </c>
-      <c r="B181" s="135" t="s">
+      <c r="B181" s="128" t="s">
         <v>196</v>
       </c>
       <c r="C181" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="106">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A182" s="102">
         <v>22068</v>
       </c>
-      <c r="B182" s="134" t="s">
+      <c r="B182" s="127" t="s">
         <v>197</v>
       </c>
       <c r="C182" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="107">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A183" s="103">
         <v>23001</v>
       </c>
-      <c r="B183" s="135" t="s">
+      <c r="B183" s="128" t="s">
         <v>198</v>
       </c>
       <c r="C183" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="107">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A184" s="103">
         <v>21002</v>
       </c>
-      <c r="B184" s="135" t="s">
+      <c r="B184" s="128" t="s">
         <v>199</v>
       </c>
       <c r="C184" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="107">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A185" s="103">
         <v>24097</v>
       </c>
-      <c r="B185" s="136" t="s">
+      <c r="B185" s="129" t="s">
         <v>200</v>
       </c>
       <c r="C185" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="107">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A186" s="103">
         <v>21003</v>
       </c>
-      <c r="B186" s="135" t="s">
+      <c r="B186" s="128" t="s">
         <v>201</v>
       </c>
       <c r="C186" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="106">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A187" s="102">
         <v>22069</v>
       </c>
-      <c r="B187" s="134" t="s">
+      <c r="B187" s="127" t="s">
         <v>202</v>
       </c>
       <c r="C187" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="107">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A188" s="103">
         <v>24098</v>
       </c>
-      <c r="B188" s="136" t="s">
+      <c r="B188" s="129" t="s">
         <v>203</v>
       </c>
       <c r="C188" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="106">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A189" s="102">
         <v>22070</v>
       </c>
-      <c r="B189" s="134" t="s">
+      <c r="B189" s="127" t="s">
         <v>204</v>
       </c>
       <c r="C189" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" s="107">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A190" s="103">
         <v>24081</v>
       </c>
-      <c r="B190" s="135" t="s">
+      <c r="B190" s="128" t="s">
         <v>205</v>
       </c>
       <c r="C190" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="108">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A191" s="104">
         <v>21007</v>
       </c>
-      <c r="B191" s="135" t="s">
+      <c r="B191" s="128" t="s">
         <v>206</v>
       </c>
       <c r="C191" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="107">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A192" s="103">
         <v>24082</v>
       </c>
-      <c r="B192" s="137" t="s">
+      <c r="B192" s="130" t="s">
         <v>207</v>
       </c>
       <c r="C192" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="106">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A193" s="102">
         <v>22071</v>
       </c>
-      <c r="B193" s="134" t="s">
+      <c r="B193" s="127" t="s">
         <v>208</v>
       </c>
       <c r="C193" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="106">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A194" s="102">
         <v>22072</v>
       </c>
-      <c r="B194" s="138" t="s">
+      <c r="B194" s="131" t="s">
         <v>209</v>
       </c>
       <c r="C194" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="107">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A195" s="103">
         <v>19028</v>
       </c>
-      <c r="B195" s="135" t="s">
+      <c r="B195" s="128" t="s">
         <v>210</v>
       </c>
       <c r="C195" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="107">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A196" s="103">
         <v>24084</v>
       </c>
-      <c r="B196" s="137" t="s">
+      <c r="B196" s="130" t="s">
         <v>211</v>
       </c>
       <c r="C196" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="106">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A197" s="102">
         <v>22074</v>
       </c>
-      <c r="B197" s="138" t="s">
+      <c r="B197" s="131" t="s">
         <v>212</v>
       </c>
       <c r="C197" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="108">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A198" s="104">
         <v>19029</v>
       </c>
-      <c r="B198" s="135" t="s">
+      <c r="B198" s="128" t="s">
         <v>213</v>
       </c>
       <c r="C198" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="107">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A199" s="103">
         <v>20010</v>
       </c>
-      <c r="B199" s="135" t="s">
+      <c r="B199" s="128" t="s">
         <v>214</v>
       </c>
       <c r="C199" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="107">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A200" s="103">
         <v>24101</v>
       </c>
-      <c r="B200" s="139" t="s">
+      <c r="B200" s="132" t="s">
         <v>215</v>
       </c>
       <c r="C200" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="106">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A201" s="102">
         <v>20091</v>
       </c>
-      <c r="B201" s="134" t="s">
+      <c r="B201" s="127" t="s">
         <v>216</v>
       </c>
       <c r="C201" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="107">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A202" s="103">
         <v>24102</v>
       </c>
-      <c r="B202" s="136" t="s">
+      <c r="B202" s="129" t="s">
         <v>217</v>
       </c>
       <c r="C202" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="107">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A203" s="103">
         <v>24087</v>
       </c>
-      <c r="B203" s="135" t="s">
+      <c r="B203" s="128" t="s">
         <v>218</v>
       </c>
       <c r="C203" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="107">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A204" s="103">
         <v>24088</v>
       </c>
-      <c r="B204" s="135" t="s">
+      <c r="B204" s="128" t="s">
         <v>219</v>
       </c>
       <c r="C204" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="107">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A205" s="103">
         <v>24103</v>
       </c>
-      <c r="B205" s="136" t="s">
+      <c r="B205" s="129" t="s">
         <v>220</v>
       </c>
       <c r="C205" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="106">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A206" s="102">
         <v>22076</v>
       </c>
-      <c r="B206" s="134" t="s">
+      <c r="B206" s="127" t="s">
         <v>221</v>
       </c>
       <c r="C206" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" s="106">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A207" s="102">
         <v>22077</v>
       </c>
-      <c r="B207" s="134" t="s">
+      <c r="B207" s="127" t="s">
         <v>222</v>
       </c>
       <c r="C207" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" s="107">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A208" s="103">
         <v>24104</v>
       </c>
-      <c r="B208" s="136" t="s">
+      <c r="B208" s="129" t="s">
         <v>223</v>
       </c>
       <c r="C208" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="107">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A209" s="103">
         <v>24105</v>
       </c>
-      <c r="B209" s="136" t="s">
+      <c r="B209" s="129" t="s">
         <v>224</v>
       </c>
       <c r="C209" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" s="107">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A210" s="103">
         <v>24089</v>
       </c>
-      <c r="B210" s="135" t="s">
+      <c r="B210" s="128" t="s">
         <v>225</v>
       </c>
       <c r="C210" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" s="106">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A211" s="102">
         <v>22078</v>
       </c>
-      <c r="B211" s="134" t="s">
+      <c r="B211" s="127" t="s">
         <v>226</v>
       </c>
       <c r="C211" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" s="106">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A212" s="102">
         <v>22079</v>
       </c>
-      <c r="B212" s="134" t="s">
+      <c r="B212" s="127" t="s">
         <v>227</v>
       </c>
       <c r="C212" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" s="107">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A213" s="103">
         <v>24106</v>
       </c>
-      <c r="B213" s="136" t="s">
+      <c r="B213" s="129" t="s">
         <v>228</v>
       </c>
       <c r="C213" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" s="106">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A214" s="102">
         <v>22080</v>
       </c>
-      <c r="B214" s="134" t="s">
+      <c r="B214" s="127" t="s">
         <v>229</v>
       </c>
       <c r="C214" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" s="107">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A215" s="103">
         <v>24107</v>
       </c>
-      <c r="B215" s="136" t="s">
+      <c r="B215" s="129" t="s">
         <v>230</v>
       </c>
       <c r="C215" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" s="107">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A216" s="103">
         <v>20089</v>
       </c>
-      <c r="B216" s="135" t="s">
+      <c r="B216" s="128" t="s">
         <v>231</v>
       </c>
       <c r="C216" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" s="107">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A217" s="103">
         <v>24108</v>
       </c>
-      <c r="B217" s="139" t="s">
+      <c r="B217" s="132" t="s">
         <v>232</v>
       </c>
       <c r="C217" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" s="107">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A218" s="103">
         <v>23025</v>
       </c>
-      <c r="B218" s="135" t="s">
+      <c r="B218" s="128" t="s">
         <v>233</v>
       </c>
       <c r="C218" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" s="106">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A219" s="102">
         <v>22081</v>
       </c>
-      <c r="B219" s="134" t="s">
+      <c r="B219" s="127" t="s">
         <v>234</v>
       </c>
       <c r="C219" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" s="106">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A220" s="102">
         <v>22093</v>
       </c>
-      <c r="B220" s="134" t="s">
+      <c r="B220" s="127" t="s">
         <v>235</v>
       </c>
       <c r="C220" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" s="106">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A221" s="102">
         <v>22082</v>
       </c>
-      <c r="B221" s="134" t="s">
+      <c r="B221" s="127" t="s">
         <v>236</v>
       </c>
       <c r="C221" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" s="107">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A222" s="103">
         <v>23026</v>
       </c>
-      <c r="B222" s="135" t="s">
+      <c r="B222" s="128" t="s">
         <v>237</v>
       </c>
       <c r="C222" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="107">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A223" s="103">
         <v>24109</v>
       </c>
-      <c r="B223" s="136" t="s">
+      <c r="B223" s="129" t="s">
         <v>238</v>
       </c>
       <c r="C223" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" s="106">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A224" s="102">
         <v>22084</v>
       </c>
-      <c r="B224" s="138" t="s">
+      <c r="B224" s="131" t="s">
         <v>239</v>
       </c>
       <c r="C224" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="107">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A225" s="103">
         <v>24110</v>
       </c>
-      <c r="B225" s="136" t="s">
+      <c r="B225" s="129" t="s">
         <v>240</v>
       </c>
       <c r="C225" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" s="107">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A226" s="103">
         <v>24111</v>
       </c>
-      <c r="B226" s="136" t="s">
+      <c r="B226" s="129" t="s">
         <v>241</v>
       </c>
       <c r="C226" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="107">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A227" s="103">
         <v>24112</v>
       </c>
-      <c r="B227" s="139" t="s">
+      <c r="B227" s="132" t="s">
         <v>242</v>
       </c>
       <c r="C227" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" s="107">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A228" s="103">
         <v>24113</v>
       </c>
-      <c r="B228" s="139" t="s">
+      <c r="B228" s="132" t="s">
         <v>243</v>
       </c>
       <c r="C228" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" s="107">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A229" s="103">
         <v>24090</v>
       </c>
-      <c r="B229" s="135" t="s">
+      <c r="B229" s="128" t="s">
         <v>244</v>
       </c>
       <c r="C229" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" s="106">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A230" s="102">
         <v>22085</v>
       </c>
-      <c r="B230" s="134" t="s">
+      <c r="B230" s="127" t="s">
         <v>245</v>
       </c>
       <c r="C230" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" s="107">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A231" s="103">
         <v>21017</v>
       </c>
-      <c r="B231" s="135" t="s">
+      <c r="B231" s="128" t="s">
         <v>246</v>
       </c>
       <c r="C231" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" s="107">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A232" s="103">
         <v>23008</v>
       </c>
-      <c r="B232" s="135" t="s">
+      <c r="B232" s="128" t="s">
         <v>247</v>
       </c>
       <c r="C232" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" s="107">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A233" s="103">
         <v>24091</v>
       </c>
-      <c r="B233" s="135" t="s">
+      <c r="B233" s="128" t="s">
         <v>248</v>
       </c>
       <c r="C233" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" s="107">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A234" s="103">
         <v>24092</v>
       </c>
-      <c r="B234" s="135" t="s">
+      <c r="B234" s="128" t="s">
         <v>249</v>
       </c>
       <c r="C234" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" s="107">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A235" s="103">
         <v>23009</v>
       </c>
-      <c r="B235" s="135" t="s">
+      <c r="B235" s="128" t="s">
         <v>250</v>
       </c>
       <c r="C235" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236" s="107">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A236" s="103">
         <v>24114</v>
       </c>
-      <c r="B236" s="136" t="s">
+      <c r="B236" s="129" t="s">
         <v>251</v>
       </c>
       <c r="C236" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A237" s="107">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A237" s="103">
         <v>21019</v>
       </c>
-      <c r="B237" s="135" t="s">
+      <c r="B237" s="128" t="s">
         <v>252</v>
       </c>
       <c r="C237" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238" s="107">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A238" s="103">
         <v>24115</v>
       </c>
-      <c r="B238" s="136" t="s">
+      <c r="B238" s="129" t="s">
         <v>253</v>
       </c>
       <c r="C238" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A239" s="106">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A239" s="102">
         <v>22086</v>
       </c>
-      <c r="B239" s="134" t="s">
+      <c r="B239" s="127" t="s">
         <v>254</v>
       </c>
       <c r="C239" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A240" s="106">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A240" s="102">
         <v>22087</v>
       </c>
-      <c r="B240" s="134" t="s">
+      <c r="B240" s="127" t="s">
         <v>255</v>
       </c>
       <c r="C240" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A241" s="106">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A241" s="102">
         <v>22088</v>
       </c>
-      <c r="B241" s="134" t="s">
+      <c r="B241" s="127" t="s">
         <v>256</v>
       </c>
       <c r="C241" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A242" s="106">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A242" s="102">
         <v>22089</v>
       </c>
-      <c r="B242" s="138" t="s">
+      <c r="B242" s="131" t="s">
         <v>257</v>
       </c>
       <c r="C242" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" s="107">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A243" s="103">
         <v>24118</v>
       </c>
-      <c r="B243" s="139" t="s">
+      <c r="B243" s="132" t="s">
         <v>258</v>
       </c>
       <c r="C243" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244" s="107">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A244" s="103">
         <v>24119</v>
       </c>
-      <c r="B244" s="136" t="s">
+      <c r="B244" s="129" t="s">
         <v>259</v>
       </c>
       <c r="C244" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245" s="106">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A245" s="102">
         <v>22090</v>
       </c>
-      <c r="B245" s="138" t="s">
+      <c r="B245" s="131" t="s">
         <v>260</v>
       </c>
       <c r="C245" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246" s="106">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A246" s="102">
         <v>22091</v>
       </c>
-      <c r="B246" s="138" t="s">
+      <c r="B246" s="131" t="s">
         <v>261</v>
       </c>
       <c r="C246" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247" s="105">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A247" s="101">
         <v>25090</v>
       </c>
-      <c r="B247" s="133" t="s">
+      <c r="B247" s="126" t="s">
         <v>262</v>
       </c>
       <c r="C247" s="92" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" s="107">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A248" s="103">
         <v>25091</v>
       </c>
-      <c r="B248" s="136" t="s">
+      <c r="B248" s="129" t="s">
         <v>264</v>
       </c>
       <c r="C248" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249" s="107">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A249" s="103">
         <v>25092</v>
       </c>
-      <c r="B249" s="136" t="s">
+      <c r="B249" s="129" t="s">
         <v>265</v>
       </c>
       <c r="C249" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250" s="107">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A250" s="103">
         <v>25093</v>
       </c>
-      <c r="B250" s="136" t="s">
+      <c r="B250" s="129" t="s">
         <v>266</v>
       </c>
       <c r="C250" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A251" s="107">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A251" s="103">
         <v>25095</v>
       </c>
-      <c r="B251" s="136" t="s">
+      <c r="B251" s="129" t="s">
         <v>267</v>
       </c>
       <c r="C251" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A252" s="107">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A252" s="103">
         <v>25096</v>
       </c>
-      <c r="B252" s="136" t="s">
+      <c r="B252" s="129" t="s">
         <v>268</v>
       </c>
       <c r="C252" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" s="107">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A253" s="103">
         <v>24099</v>
       </c>
-      <c r="B253" s="136" t="s">
+      <c r="B253" s="129" t="s">
         <v>269</v>
       </c>
       <c r="C253" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" s="107">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A254" s="103">
         <v>25097</v>
       </c>
-      <c r="B254" s="136" t="s">
+      <c r="B254" s="129" t="s">
         <v>270</v>
       </c>
       <c r="C254" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A255" s="107">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A255" s="103">
         <v>25098</v>
       </c>
-      <c r="B255" s="136" t="s">
+      <c r="B255" s="129" t="s">
         <v>271</v>
       </c>
       <c r="C255" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256" s="107">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A256" s="103">
         <v>24100</v>
       </c>
-      <c r="B256" s="136" t="s">
+      <c r="B256" s="129" t="s">
         <v>272</v>
       </c>
       <c r="C256" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" s="107">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A257" s="103">
         <v>25100</v>
       </c>
-      <c r="B257" s="140" t="s">
+      <c r="B257" s="133" t="s">
         <v>273</v>
       </c>
       <c r="C257" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258" s="107">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A258" s="103">
         <v>25101</v>
       </c>
-      <c r="B258" s="136" t="s">
+      <c r="B258" s="129" t="s">
         <v>274</v>
       </c>
       <c r="C258" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259" s="107">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A259" s="103">
         <v>25102</v>
       </c>
-      <c r="B259" s="136" t="s">
+      <c r="B259" s="129" t="s">
         <v>275</v>
       </c>
       <c r="C259" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260" s="107">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A260" s="103">
         <v>25103</v>
       </c>
-      <c r="B260" s="136" t="s">
+      <c r="B260" s="129" t="s">
         <v>276</v>
       </c>
       <c r="C260" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261" s="107">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A261" s="103">
         <v>25105</v>
       </c>
-      <c r="B261" s="136" t="s">
+      <c r="B261" s="129" t="s">
         <v>277</v>
       </c>
       <c r="C261" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262" s="107">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A262" s="103">
         <v>25106</v>
       </c>
-      <c r="B262" s="136" t="s">
+      <c r="B262" s="129" t="s">
         <v>278</v>
       </c>
       <c r="C262" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" s="107">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A263" s="103">
         <v>25107</v>
       </c>
-      <c r="B263" s="136" t="s">
+      <c r="B263" s="129" t="s">
         <v>279</v>
       </c>
       <c r="C263" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A264" s="107">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A264" s="103">
         <v>25110</v>
       </c>
-      <c r="B264" s="136" t="s">
+      <c r="B264" s="129" t="s">
         <v>280</v>
       </c>
       <c r="C264" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265" s="107">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A265" s="103">
         <v>25111</v>
       </c>
-      <c r="B265" s="136" t="s">
+      <c r="B265" s="129" t="s">
         <v>281</v>
       </c>
       <c r="C265" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266" s="107">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A266" s="103">
         <v>25112</v>
       </c>
-      <c r="B266" s="136" t="s">
+      <c r="B266" s="129" t="s">
         <v>282</v>
       </c>
       <c r="C266" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267" s="107">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A267" s="103">
         <v>25113</v>
       </c>
-      <c r="B267" s="136" t="s">
+      <c r="B267" s="129" t="s">
         <v>283</v>
       </c>
       <c r="C267" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268" s="107">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A268" s="103">
         <v>25116</v>
       </c>
-      <c r="B268" s="136" t="s">
+      <c r="B268" s="129" t="s">
         <v>284</v>
       </c>
       <c r="C268" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269" s="107">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A269" s="103">
         <v>25118</v>
       </c>
-      <c r="B269" s="136" t="s">
+      <c r="B269" s="129" t="s">
         <v>285</v>
       </c>
       <c r="C269" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A270" s="107">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A270" s="103">
         <v>25120</v>
       </c>
-      <c r="B270" s="136" t="s">
+      <c r="B270" s="129" t="s">
         <v>286</v>
       </c>
       <c r="C270" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271" s="107">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A271" s="103">
         <v>25122</v>
       </c>
-      <c r="B271" s="136" t="s">
+      <c r="B271" s="129" t="s">
         <v>287</v>
       </c>
       <c r="C271" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A272" s="107">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A272" s="103">
         <v>25123</v>
       </c>
-      <c r="B272" s="136" t="s">
+      <c r="B272" s="129" t="s">
         <v>288</v>
       </c>
       <c r="C272" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A273" s="109">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A273" s="105">
         <v>21023</v>
       </c>
-      <c r="B273" s="141" t="s">
+      <c r="B273" s="134" t="s">
         <v>289</v>
       </c>
       <c r="C273" s="92" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A274" s="110">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A274" s="106">
         <v>22001</v>
       </c>
-      <c r="B274" s="142" t="s">
+      <c r="B274" s="135" t="s">
         <v>291</v>
       </c>
       <c r="C274" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A275" s="110">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A275" s="106">
         <v>21024</v>
       </c>
-      <c r="B275" s="142" t="s">
+      <c r="B275" s="135" t="s">
         <v>292</v>
       </c>
       <c r="C275" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A276" s="110">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A276" s="106">
         <v>23018</v>
       </c>
-      <c r="B276" s="142" t="s">
+      <c r="B276" s="135" t="s">
         <v>293</v>
       </c>
       <c r="C276" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A277" s="110">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A277" s="106">
         <v>22003</v>
       </c>
-      <c r="B277" s="142" t="s">
+      <c r="B277" s="135" t="s">
         <v>294</v>
       </c>
       <c r="C277" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A278" s="110">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A278" s="106">
         <v>23002</v>
       </c>
-      <c r="B278" s="142" t="s">
+      <c r="B278" s="135" t="s">
         <v>295</v>
       </c>
       <c r="C278" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A279" s="110">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A279" s="106">
         <v>22026</v>
       </c>
-      <c r="B279" s="142" t="s">
+      <c r="B279" s="135" t="s">
         <v>296</v>
       </c>
       <c r="C279" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A280" s="110">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A280" s="106">
         <v>20024</v>
       </c>
-      <c r="B280" s="142" t="s">
+      <c r="B280" s="135" t="s">
         <v>297</v>
       </c>
       <c r="C280" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281" s="110">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A281" s="106">
         <v>23006</v>
       </c>
-      <c r="B281" s="142" t="s">
+      <c r="B281" s="135" t="s">
         <v>298</v>
       </c>
       <c r="C281" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282" s="110">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A282" s="106">
         <v>22006</v>
       </c>
-      <c r="B282" s="142" t="s">
+      <c r="B282" s="135" t="s">
         <v>299</v>
       </c>
       <c r="C282" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283" s="110">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A283" s="106">
         <v>21029</v>
       </c>
-      <c r="B283" s="142" t="s">
+      <c r="B283" s="135" t="s">
         <v>300</v>
       </c>
       <c r="C283" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A284" s="110">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A284" s="106">
         <v>23023</v>
       </c>
-      <c r="B284" s="142" t="s">
+      <c r="B284" s="135" t="s">
         <v>301</v>
       </c>
       <c r="C284" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A285" s="110">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A285" s="106">
         <v>23027</v>
       </c>
-      <c r="B285" s="142" t="s">
+      <c r="B285" s="135" t="s">
         <v>302</v>
       </c>
       <c r="C285" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A286" s="110">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A286" s="106">
         <v>23028</v>
       </c>
-      <c r="B286" s="142" t="s">
+      <c r="B286" s="135" t="s">
         <v>303</v>
       </c>
       <c r="C286" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A287" s="110">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A287" s="106">
         <v>22025</v>
       </c>
-      <c r="B287" s="142" t="s">
+      <c r="B287" s="135" t="s">
         <v>304</v>
       </c>
       <c r="C287" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A288" s="110">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A288" s="106">
         <v>21031</v>
       </c>
-      <c r="B288" s="142" t="s">
+      <c r="B288" s="135" t="s">
         <v>305</v>
       </c>
       <c r="C288" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A289" s="110">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A289" s="106">
         <v>23031</v>
       </c>
-      <c r="B289" s="142" t="s">
+      <c r="B289" s="135" t="s">
         <v>306</v>
       </c>
       <c r="C289" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A290" s="110">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A290" s="106">
         <v>21034</v>
       </c>
-      <c r="B290" s="142" t="s">
+      <c r="B290" s="135" t="s">
         <v>307</v>
       </c>
       <c r="C290" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A291" s="110">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A291" s="106">
         <v>22018</v>
       </c>
-      <c r="B291" s="142" t="s">
+      <c r="B291" s="135" t="s">
         <v>308</v>
       </c>
       <c r="C291" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A292" s="110">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A292" s="106">
         <v>22019</v>
       </c>
-      <c r="B292" s="142" t="s">
+      <c r="B292" s="135" t="s">
         <v>309</v>
       </c>
       <c r="C292" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A293" s="110">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A293" s="106">
         <v>20025</v>
       </c>
-      <c r="B293" s="142" t="s">
+      <c r="B293" s="135" t="s">
         <v>310</v>
       </c>
       <c r="C293" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A294" s="105">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A294" s="101">
         <v>21022</v>
       </c>
-      <c r="B294" s="143" t="s">
+      <c r="B294" s="136" t="s">
         <v>311</v>
       </c>
       <c r="C294" s="92" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A295" s="107">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A295" s="103">
         <v>21025</v>
       </c>
-      <c r="B295" s="135" t="s">
+      <c r="B295" s="128" t="s">
         <v>313</v>
       </c>
       <c r="C295" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A296" s="111">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A296" s="107">
         <v>23015</v>
       </c>
-      <c r="B296" s="135" t="s">
+      <c r="B296" s="128" t="s">
         <v>314</v>
       </c>
       <c r="C296" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A297" s="107">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A297" s="103">
         <v>23004</v>
       </c>
-      <c r="B297" s="135" t="s">
+      <c r="B297" s="128" t="s">
         <v>315</v>
       </c>
       <c r="C297" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A298" s="107">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A298" s="103">
         <v>22004</v>
       </c>
-      <c r="B298" s="135" t="s">
+      <c r="B298" s="128" t="s">
         <v>316</v>
       </c>
       <c r="C298" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A299" s="107">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A299" s="103">
         <v>23005</v>
       </c>
-      <c r="B299" s="135" t="s">
+      <c r="B299" s="128" t="s">
         <v>317</v>
       </c>
       <c r="C299" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A300" s="107">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A300" s="103">
         <v>21026</v>
       </c>
-      <c r="B300" s="135" t="s">
+      <c r="B300" s="128" t="s">
         <v>318</v>
       </c>
       <c r="C300" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A301" s="107">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A301" s="103">
         <v>22005</v>
       </c>
-      <c r="B301" s="135" t="s">
+      <c r="B301" s="128" t="s">
         <v>319</v>
       </c>
       <c r="C301" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A302" s="107">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A302" s="103">
         <v>22075</v>
       </c>
-      <c r="B302" s="135" t="s">
+      <c r="B302" s="128" t="s">
         <v>320</v>
       </c>
       <c r="C302" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A303" s="107">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A303" s="103">
         <v>21011</v>
       </c>
-      <c r="B303" s="135" t="s">
+      <c r="B303" s="128" t="s">
         <v>321</v>
       </c>
       <c r="C303" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A304" s="107">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A304" s="103">
         <v>23020</v>
       </c>
-      <c r="B304" s="135" t="s">
+      <c r="B304" s="128" t="s">
         <v>322</v>
       </c>
       <c r="C304" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A305" s="112">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A305" s="108">
         <v>21030</v>
       </c>
-      <c r="B305" s="135" t="s">
+      <c r="B305" s="128" t="s">
         <v>323</v>
       </c>
       <c r="C305" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A306" s="107">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A306" s="103">
         <v>22011</v>
       </c>
-      <c r="B306" s="135" t="s">
+      <c r="B306" s="128" t="s">
         <v>324</v>
       </c>
       <c r="C306" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A307" s="107">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A307" s="103">
         <v>22034</v>
       </c>
-      <c r="B307" s="135" t="s">
+      <c r="B307" s="128" t="s">
         <v>325</v>
       </c>
       <c r="C307" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A308" s="107">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A308" s="103">
         <v>22012</v>
       </c>
-      <c r="B308" s="135" t="s">
+      <c r="B308" s="128" t="s">
         <v>326</v>
       </c>
       <c r="C308" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A309" s="107">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A309" s="103">
         <v>18080</v>
       </c>
-      <c r="B309" s="135" t="s">
+      <c r="B309" s="128" t="s">
         <v>327</v>
       </c>
       <c r="C309" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A310" s="107">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A310" s="103">
         <v>22014</v>
       </c>
-      <c r="B310" s="135" t="s">
+      <c r="B310" s="128" t="s">
         <v>328</v>
       </c>
       <c r="C310" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A311" s="107">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A311" s="103">
         <v>23007</v>
       </c>
-      <c r="B311" s="135" t="s">
+      <c r="B311" s="128" t="s">
         <v>329</v>
       </c>
       <c r="C311" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A312" s="107">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A312" s="103">
         <v>21035</v>
       </c>
-      <c r="B312" s="135" t="s">
+      <c r="B312" s="128" t="s">
         <v>330</v>
       </c>
       <c r="C312" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A313" s="107">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A313" s="103">
         <v>23012</v>
       </c>
-      <c r="B313" s="135" t="s">
+      <c r="B313" s="128" t="s">
         <v>331</v>
       </c>
       <c r="C313" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A314" s="107">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A314" s="103">
         <v>23013</v>
       </c>
-      <c r="B314" s="135" t="s">
+      <c r="B314" s="128" t="s">
         <v>332</v>
       </c>
       <c r="C314" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A315" s="107">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A315" s="103">
         <v>22017</v>
       </c>
-      <c r="B315" s="135" t="s">
+      <c r="B315" s="128" t="s">
         <v>333</v>
       </c>
       <c r="C315" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A316" s="107">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A316" s="103">
         <v>20072</v>
       </c>
-      <c r="B316" s="135" t="s">
+      <c r="B316" s="128" t="s">
         <v>334</v>
       </c>
       <c r="C316" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A317" s="107">
+    <row r="317" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A317" s="103">
         <v>21040</v>
       </c>
-      <c r="B317" s="135" t="s">
+      <c r="B317" s="128" t="s">
         <v>335</v>
       </c>
       <c r="C317" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A318" s="113">
+    <row r="318" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A318" s="109">
         <v>20080</v>
       </c>
-      <c r="B318" s="144" t="s">
+      <c r="B318" s="137" t="s">
         <v>336</v>
       </c>
       <c r="C318" s="92" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A319" s="114">
+    <row r="319" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A319" s="110">
         <v>23019</v>
       </c>
-      <c r="B319" s="145" t="s">
+      <c r="B319" s="138" t="s">
         <v>338</v>
       </c>
       <c r="C319" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A320" s="114">
+    <row r="320" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A320" s="110">
         <v>23021</v>
       </c>
-      <c r="B320" s="145" t="s">
+      <c r="B320" s="138" t="s">
         <v>339</v>
       </c>
       <c r="C320" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A321" s="114">
+    <row r="321" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A321" s="110">
         <v>21028</v>
       </c>
-      <c r="B321" s="145" t="s">
+      <c r="B321" s="138" t="s">
         <v>340</v>
       </c>
       <c r="C321" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A322" s="114">
+    <row r="322" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A322" s="110">
         <v>23022</v>
       </c>
-      <c r="B322" s="145" t="s">
+      <c r="B322" s="138" t="s">
         <v>341</v>
       </c>
       <c r="C322" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A323" s="114">
+    <row r="323" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A323" s="110">
         <v>23030</v>
       </c>
-      <c r="B323" s="145" t="s">
+      <c r="B323" s="138" t="s">
         <v>342</v>
       </c>
       <c r="C323" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A324" s="114">
+    <row r="324" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A324" s="110">
         <v>21032</v>
       </c>
-      <c r="B324" s="146" t="s">
+      <c r="B324" s="139" t="s">
         <v>343</v>
       </c>
       <c r="C324" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A325" s="114">
+    <row r="325" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A325" s="110">
         <v>23010</v>
       </c>
-      <c r="B325" s="146" t="s">
+      <c r="B325" s="139" t="s">
         <v>344</v>
       </c>
       <c r="C325" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A326" s="114">
+    <row r="326" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A326" s="110">
         <v>23032</v>
       </c>
-      <c r="B326" s="145" t="s">
+      <c r="B326" s="138" t="s">
         <v>345</v>
       </c>
       <c r="C326" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A327" s="114">
+    <row r="327" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A327" s="110">
         <v>21036</v>
       </c>
-      <c r="B327" s="145" t="s">
+      <c r="B327" s="138" t="s">
         <v>346</v>
       </c>
       <c r="C327" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A328" s="114">
+    <row r="328" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A328" s="110">
         <v>23014</v>
       </c>
-      <c r="B328" s="145" t="s">
+      <c r="B328" s="138" t="s">
         <v>347</v>
       </c>
       <c r="C328" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A329" s="114">
+    <row r="329" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A329" s="110">
         <v>23035</v>
       </c>
-      <c r="B329" s="145" t="s">
+      <c r="B329" s="138" t="s">
         <v>348</v>
       </c>
       <c r="C329" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A330" s="115">
+    <row r="330" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A330" s="111">
         <v>25074</v>
       </c>
-      <c r="B330" s="116" t="s">
+      <c r="B330" s="112" t="s">
         <v>349</v>
       </c>
       <c r="C330" s="92" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A331" s="117">
+    <row r="331" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A331" s="113">
         <v>24080</v>
       </c>
-      <c r="B331" s="118" t="s">
+      <c r="B331" s="114" t="s">
         <v>351</v>
       </c>
       <c r="C331" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A332" s="119">
+    <row r="332" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A332" s="115">
         <v>25075</v>
       </c>
-      <c r="B332" s="118" t="s">
+      <c r="B332" s="114" t="s">
         <v>352</v>
       </c>
       <c r="C332" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A333" s="117">
+    <row r="333" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A333" s="113">
         <v>22046</v>
       </c>
-      <c r="B333" s="120" t="s">
+      <c r="B333" s="116" t="s">
         <v>353</v>
       </c>
       <c r="C333" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A334" s="117">
+    <row r="334" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A334" s="113">
         <v>25076</v>
       </c>
-      <c r="B334" s="120" t="s">
+      <c r="B334" s="116" t="s">
         <v>354</v>
       </c>
       <c r="C334" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A335" s="117">
+    <row r="335" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A335" s="113">
         <v>22047</v>
       </c>
-      <c r="B335" s="120" t="s">
+      <c r="B335" s="116" t="s">
         <v>355</v>
       </c>
       <c r="C335" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A336" s="117">
+    <row r="336" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A336" s="113">
         <v>25077</v>
       </c>
-      <c r="B336" s="120" t="s">
+      <c r="B336" s="116" t="s">
         <v>356</v>
       </c>
       <c r="C336" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A337" s="117">
+    <row r="337" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A337" s="113">
         <v>22052</v>
       </c>
-      <c r="B337" s="120" t="s">
+      <c r="B337" s="116" t="s">
         <v>357</v>
       </c>
       <c r="C337" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A338" s="117">
+    <row r="338" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A338" s="113">
         <v>25078</v>
       </c>
-      <c r="B338" s="120" t="s">
+      <c r="B338" s="116" t="s">
         <v>358</v>
       </c>
       <c r="C338" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A339" s="117">
+    <row r="339" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A339" s="113">
         <v>25079</v>
       </c>
-      <c r="B339" s="120" t="s">
+      <c r="B339" s="116" t="s">
         <v>359</v>
       </c>
       <c r="C339" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A340" s="117">
+    <row r="340" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A340" s="113">
         <v>24086</v>
       </c>
-      <c r="B340" s="120" t="s">
+      <c r="B340" s="116" t="s">
         <v>360</v>
       </c>
       <c r="C340" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A341" s="117">
+    <row r="341" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A341" s="113">
         <v>25083</v>
       </c>
-      <c r="B341" s="120" t="s">
+      <c r="B341" s="116" t="s">
         <v>361</v>
       </c>
       <c r="C341" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A342" s="117">
+    <row r="342" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A342" s="113">
         <v>25083</v>
       </c>
-      <c r="B342" s="120" t="s">
+      <c r="B342" s="116" t="s">
         <v>362</v>
       </c>
       <c r="C342" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A343" s="117">
+    <row r="343" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A343" s="113">
         <v>22058</v>
       </c>
-      <c r="B343" s="120" t="s">
+      <c r="B343" s="116" t="s">
         <v>363</v>
       </c>
       <c r="C343" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A344" s="117">
+    <row r="344" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A344" s="113">
         <v>22059</v>
       </c>
-      <c r="B344" s="120" t="s">
+      <c r="B344" s="116" t="s">
         <v>364</v>
       </c>
       <c r="C344" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A345" s="117">
+    <row r="345" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A345" s="113">
         <v>25085</v>
       </c>
-      <c r="B345" s="120" t="s">
+      <c r="B345" s="116" t="s">
         <v>365</v>
       </c>
       <c r="C345" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A346" s="117">
+    <row r="346" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A346" s="113">
         <v>20019</v>
       </c>
-      <c r="B346" s="120" t="s">
+      <c r="B346" s="116" t="s">
         <v>366</v>
       </c>
       <c r="C346" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="347" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A347" s="117">
+    <row r="347" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A347" s="113">
         <v>22060</v>
       </c>
-      <c r="B347" s="121" t="s">
+      <c r="B347" s="117" t="s">
         <v>367</v>
       </c>
       <c r="C347" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A348" s="117">
+    <row r="348" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A348" s="113">
         <v>25086</v>
       </c>
-      <c r="B348" s="121" t="s">
+      <c r="B348" s="117" t="s">
         <v>368</v>
       </c>
       <c r="C348" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A349" s="117">
+    <row r="349" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A349" s="113">
         <v>25087</v>
       </c>
-      <c r="B349" s="121" t="s">
+      <c r="B349" s="117" t="s">
         <v>369</v>
       </c>
       <c r="C349" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A350" s="117">
+    <row r="350" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A350" s="113">
         <v>22061</v>
       </c>
-      <c r="B350" s="120" t="s">
+      <c r="B350" s="116" t="s">
         <v>370</v>
       </c>
       <c r="C350" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A351" s="117">
+    <row r="351" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A351" s="113">
         <v>18069</v>
       </c>
-      <c r="B351" s="120" t="s">
+      <c r="B351" s="116" t="s">
         <v>371</v>
       </c>
       <c r="C351" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A352" s="117">
+    <row r="352" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A352" s="113">
         <v>24093</v>
       </c>
-      <c r="B352" s="120" t="s">
+      <c r="B352" s="116" t="s">
         <v>372</v>
       </c>
       <c r="C352" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A353" s="117">
+    <row r="353" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A353" s="113">
         <v>22066</v>
       </c>
-      <c r="B353" s="120" t="s">
+      <c r="B353" s="116" t="s">
         <v>373</v>
       </c>
       <c r="C353" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A354" s="117">
+    <row r="354" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A354" s="113">
         <v>25089</v>
       </c>
-      <c r="B354" s="118" t="s">
+      <c r="B354" s="114" t="s">
         <v>374</v>
       </c>
       <c r="C354" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A355" s="99">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A355" s="95">
         <v>24144</v>
       </c>
-      <c r="B355" s="147" t="s">
+      <c r="B355" s="140" t="s">
         <v>375</v>
       </c>
       <c r="C355" s="92" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A356" s="100">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A356" s="96">
         <v>24123</v>
       </c>
-      <c r="B356" s="148" t="s">
+      <c r="B356" s="141" t="s">
         <v>377</v>
       </c>
       <c r="C356" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A357" s="100">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A357" s="96">
         <v>25125</v>
       </c>
-      <c r="B357" s="148" t="s">
+      <c r="B357" s="141" t="s">
         <v>378</v>
       </c>
       <c r="C357" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A358" s="100">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A358" s="96">
         <v>24129</v>
       </c>
-      <c r="B358" s="148" t="s">
+      <c r="B358" s="141" t="s">
         <v>379</v>
       </c>
       <c r="C358" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A359" s="100">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A359" s="96">
         <v>25126</v>
       </c>
-      <c r="B359" s="148" t="s">
+      <c r="B359" s="141" t="s">
         <v>380</v>
       </c>
       <c r="C359" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A360" s="100">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A360" s="96">
         <v>24134</v>
       </c>
-      <c r="B360" s="148" t="s">
+      <c r="B360" s="141" t="s">
         <v>381</v>
       </c>
       <c r="C360" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A361" s="100">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A361" s="96">
         <v>25127</v>
       </c>
-      <c r="B361" s="148" t="s">
+      <c r="B361" s="141" t="s">
         <v>382</v>
       </c>
       <c r="C361" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A362" s="100">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A362" s="96">
         <v>25128</v>
       </c>
-      <c r="B362" s="148" t="s">
+      <c r="B362" s="141" t="s">
         <v>383</v>
       </c>
       <c r="C362" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A363" s="100">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A363" s="96">
         <v>25129</v>
       </c>
-      <c r="B363" s="148" t="s">
+      <c r="B363" s="141" t="s">
         <v>384</v>
       </c>
       <c r="C363" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A364" s="100">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A364" s="96">
         <v>25130</v>
       </c>
-      <c r="B364" s="148" t="s">
+      <c r="B364" s="141" t="s">
         <v>385</v>
       </c>
       <c r="C364" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A365" s="100">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A365" s="96">
         <v>25131</v>
       </c>
-      <c r="B365" s="148" t="s">
+      <c r="B365" s="141" t="s">
         <v>386</v>
       </c>
       <c r="C365" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A366" s="100">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A366" s="96">
         <v>25132</v>
       </c>
-      <c r="B366" s="148" t="s">
+      <c r="B366" s="141" t="s">
         <v>387</v>
       </c>
       <c r="C366" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A367" s="100">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A367" s="96">
         <v>24122</v>
       </c>
-      <c r="B367" s="148" t="s">
+      <c r="B367" s="141" t="s">
         <v>388</v>
       </c>
       <c r="C367" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A368" s="100">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A368" s="96">
         <v>25133</v>
       </c>
-      <c r="B368" s="148" t="s">
+      <c r="B368" s="141" t="s">
         <v>389</v>
       </c>
       <c r="C368" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A369" s="100">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A369" s="96">
         <v>24143</v>
       </c>
-      <c r="B369" s="148" t="s">
+      <c r="B369" s="141" t="s">
         <v>390</v>
       </c>
       <c r="C369" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A370" s="100">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A370" s="96">
         <v>25134</v>
       </c>
-      <c r="B370" s="148" t="s">
+      <c r="B370" s="141" t="s">
         <v>391</v>
       </c>
       <c r="C370" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A371" s="100">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A371" s="96">
         <v>24138</v>
       </c>
-      <c r="B371" s="148" t="s">
+      <c r="B371" s="141" t="s">
         <v>392</v>
       </c>
       <c r="C371" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A372" s="100">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A372" s="96">
         <v>25135</v>
       </c>
-      <c r="B372" s="148" t="s">
+      <c r="B372" s="141" t="s">
         <v>393</v>
       </c>
       <c r="C372" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A373" s="100">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A373" s="96">
         <v>25136</v>
       </c>
-      <c r="B373" s="148" t="s">
+      <c r="B373" s="141" t="s">
         <v>394</v>
       </c>
       <c r="C373" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A374" s="100">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A374" s="96">
         <v>25137</v>
       </c>
-      <c r="B374" s="148" t="s">
+      <c r="B374" s="141" t="s">
         <v>395</v>
       </c>
       <c r="C374" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A375" s="100">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A375" s="96">
         <v>25138</v>
       </c>
-      <c r="B375" s="148" t="s">
+      <c r="B375" s="141" t="s">
         <v>396</v>
       </c>
       <c r="C375" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A376" s="100">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A376" s="96">
         <v>25141</v>
       </c>
-      <c r="B376" s="148" t="s">
+      <c r="B376" s="141" t="s">
         <v>397</v>
       </c>
       <c r="C376" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A377" s="100">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A377" s="96">
         <v>24148</v>
       </c>
-      <c r="B377" s="148" t="s">
+      <c r="B377" s="141" t="s">
         <v>398</v>
       </c>
       <c r="C377" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A378" s="100">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A378" s="96">
         <v>25139</v>
       </c>
-      <c r="B378" s="148" t="s">
+      <c r="B378" s="141" t="s">
         <v>399</v>
       </c>
       <c r="C378" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A379" s="100">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A379" s="96">
         <v>25140</v>
       </c>
-      <c r="B379" s="148" t="s">
+      <c r="B379" s="141" t="s">
         <v>400</v>
       </c>
       <c r="C379" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A380" s="122">
+    <row r="380" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A380" s="118">
         <v>25030</v>
       </c>
-      <c r="B380" s="126" t="s">
+      <c r="B380" s="122" t="s">
         <v>401</v>
       </c>
       <c r="C380" s="92" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A381" s="123">
+    <row r="381" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A381" s="119">
         <v>25007</v>
       </c>
       <c r="B381" s="90" t="s">
@@ -7704,8 +7771,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="382" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A382" s="123">
+    <row r="382" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A382" s="119">
         <v>25011</v>
       </c>
       <c r="B382" s="90" t="s">
@@ -7715,8 +7782,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A383" s="123">
+    <row r="383" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A383" s="119">
         <v>25016</v>
       </c>
       <c r="B383" s="90" t="s">
@@ -7726,8 +7793,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A384" s="123">
+    <row r="384" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A384" s="119">
         <v>25017</v>
       </c>
       <c r="B384" s="90" t="s">
@@ -7737,8 +7804,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A385" s="123">
+    <row r="385" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A385" s="119">
         <v>25028</v>
       </c>
       <c r="B385" s="90" t="s">
@@ -7748,8 +7815,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="386" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A386" s="123">
+    <row r="386" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A386" s="119">
         <v>25032</v>
       </c>
       <c r="B386" s="90" t="s">
@@ -7759,8 +7826,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="387" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A387" s="123">
+    <row r="387" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A387" s="119">
         <v>25041</v>
       </c>
       <c r="B387" s="90" t="s">
@@ -7770,8 +7837,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="388" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A388" s="123">
+    <row r="388" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A388" s="119">
         <v>25046</v>
       </c>
       <c r="B388" s="90" t="s">
@@ -7781,8 +7848,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="389" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A389" s="123">
+    <row r="389" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A389" s="119">
         <v>25060</v>
       </c>
       <c r="B389" s="90" t="s">
@@ -7792,8 +7859,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="390" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A390" s="123">
+    <row r="390" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A390" s="119">
         <v>25064</v>
       </c>
       <c r="B390" s="90" t="s">
@@ -7803,8 +7870,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="391" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A391" s="123">
+    <row r="391" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A391" s="119">
         <v>25066</v>
       </c>
       <c r="B391" s="90" t="s">
@@ -7814,8 +7881,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A392" s="123">
+    <row r="392" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A392" s="119">
         <v>25067</v>
       </c>
       <c r="B392" s="90" t="s">
@@ -7825,8 +7892,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="393" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A393" s="123">
+    <row r="393" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A393" s="119">
         <v>25071</v>
       </c>
       <c r="B393" s="90" t="s">
@@ -7836,8 +7903,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="394" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A394" s="123">
+    <row r="394" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A394" s="119">
         <v>25081</v>
       </c>
       <c r="B394" s="90" t="s">
@@ -7847,8 +7914,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="395" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A395" s="123">
+    <row r="395" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A395" s="119">
         <v>25084</v>
       </c>
       <c r="B395" s="90" t="s">
@@ -7858,8 +7925,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="396" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A396" s="123">
+    <row r="396" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A396" s="119">
         <v>25088</v>
       </c>
       <c r="B396" s="90" t="s">
@@ -7869,8 +7936,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="397" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A397" s="123">
+    <row r="397" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A397" s="119">
         <v>25094</v>
       </c>
       <c r="B397" s="90" t="s">
@@ -7880,8 +7947,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="398" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A398" s="123">
+    <row r="398" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A398" s="119">
         <v>25099</v>
       </c>
       <c r="B398" s="90" t="s">
@@ -7891,8 +7958,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="399" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A399" s="123">
+    <row r="399" spans="1:3" ht="17" x14ac:dyDescent="0.45">
+      <c r="A399" s="119">
         <v>25104</v>
       </c>
       <c r="B399" s="90" t="s">
@@ -7902,209 +7969,209 @@
         <v>402</v>
       </c>
     </row>
-    <row r="400" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A400" s="91">
         <v>24120</v>
       </c>
-      <c r="B400" s="147" t="s">
+      <c r="B400" s="140" t="s">
         <v>422</v>
       </c>
       <c r="C400" s="92" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A401" s="124">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A401" s="120">
         <v>24125</v>
       </c>
-      <c r="B401" s="148" t="s">
+      <c r="B401" s="141" t="s">
         <v>424</v>
       </c>
       <c r="C401" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A402" s="103">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A402" s="99">
         <v>24126</v>
       </c>
-      <c r="B402" s="148" t="s">
+      <c r="B402" s="141" t="s">
         <v>425</v>
       </c>
       <c r="C402" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A403" s="103">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A403" s="99">
         <v>24128</v>
       </c>
-      <c r="B403" s="148" t="s">
+      <c r="B403" s="141" t="s">
         <v>426</v>
       </c>
       <c r="C403" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A404" s="124">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A404" s="120">
         <v>24127</v>
       </c>
-      <c r="B404" s="148" t="s">
+      <c r="B404" s="141" t="s">
         <v>427</v>
       </c>
       <c r="C404" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A405" s="124">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A405" s="120">
         <v>24131</v>
       </c>
-      <c r="B405" s="148" t="s">
+      <c r="B405" s="141" t="s">
         <v>428</v>
       </c>
       <c r="C405" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A406" s="103">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A406" s="99">
         <v>24132</v>
       </c>
-      <c r="B406" s="148" t="s">
+      <c r="B406" s="141" t="s">
         <v>429</v>
       </c>
       <c r="C406" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A407" s="124">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A407" s="120">
         <v>24121</v>
       </c>
-      <c r="B407" s="148" t="s">
+      <c r="B407" s="141" t="s">
         <v>430</v>
       </c>
       <c r="C407" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A408" s="124">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A408" s="120">
         <v>24135</v>
       </c>
-      <c r="B408" s="148" t="s">
+      <c r="B408" s="141" t="s">
         <v>431</v>
       </c>
       <c r="C408" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A409" s="103">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A409" s="99">
         <v>24136</v>
       </c>
-      <c r="B409" s="148" t="s">
+      <c r="B409" s="141" t="s">
         <v>432</v>
       </c>
       <c r="C409" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A410" s="124">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A410" s="120">
         <v>24137</v>
       </c>
-      <c r="B410" s="148" t="s">
+      <c r="B410" s="141" t="s">
         <v>433</v>
       </c>
       <c r="C410" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A411" s="124">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A411" s="120">
         <v>24139</v>
       </c>
-      <c r="B411" s="148" t="s">
+      <c r="B411" s="141" t="s">
         <v>434</v>
       </c>
       <c r="C411" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A412" s="103">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A412" s="99">
         <v>24140</v>
       </c>
-      <c r="B412" s="148" t="s">
+      <c r="B412" s="141" t="s">
         <v>435</v>
       </c>
       <c r="C412" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A413" s="124">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A413" s="120">
         <v>24141</v>
       </c>
-      <c r="B413" s="148" t="s">
+      <c r="B413" s="141" t="s">
         <v>436</v>
       </c>
       <c r="C413" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A414" s="103">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A414" s="99">
         <v>24142</v>
       </c>
-      <c r="B414" s="148" t="s">
+      <c r="B414" s="141" t="s">
         <v>437</v>
       </c>
       <c r="C414" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A415" s="124">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A415" s="120">
         <v>24145</v>
       </c>
-      <c r="B415" s="148" t="s">
+      <c r="B415" s="141" t="s">
         <v>438</v>
       </c>
       <c r="C415" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A416" s="124">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A416" s="120">
         <v>24147</v>
       </c>
-      <c r="B416" s="148" t="s">
+      <c r="B416" s="141" t="s">
         <v>439</v>
       </c>
       <c r="C416" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A417" s="103">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A417" s="99">
         <v>20023</v>
       </c>
-      <c r="B417" s="149" t="s">
+      <c r="B417" s="142" t="s">
         <v>440</v>
       </c>
       <c r="C417" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A418" s="103">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A418" s="99">
         <v>24149</v>
       </c>
-      <c r="B418" s="148" t="s">
+      <c r="B418" s="141" t="s">
         <v>441</v>
       </c>
       <c r="C418" t="s">
@@ -8112,7 +8179,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C418" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8120,13 +8186,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C306"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="75.42578125" customWidth="1"/>
-    <col min="3" max="3" width="39.42578125" customWidth="1"/>
+    <col min="2" max="2" width="75.453125" customWidth="1"/>
+    <col min="3" max="3" width="39.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8137,7 +8203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -8148,7 +8214,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -8159,7 +8225,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
@@ -8170,7 +8236,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
@@ -8181,7 +8247,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
@@ -8192,7 +8258,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>10</v>
       </c>
@@ -8203,7 +8269,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -8214,7 +8280,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
@@ -8225,7 +8291,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -8236,7 +8302,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
@@ -8247,7 +8313,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
@@ -8258,7 +8324,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>10</v>
       </c>
@@ -8269,7 +8335,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>10</v>
       </c>
@@ -8280,7 +8346,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="20" t="s">
         <v>38</v>
       </c>
@@ -8291,7 +8357,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="20" t="s">
         <v>38</v>
       </c>
@@ -8302,7 +8368,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="20" t="s">
         <v>38</v>
       </c>
@@ -8313,7 +8379,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="20" t="s">
         <v>38</v>
       </c>
@@ -8324,7 +8390,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="20" t="s">
         <v>38</v>
       </c>
@@ -8335,7 +8401,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="20" t="s">
         <v>38</v>
       </c>
@@ -8346,7 +8412,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="20" t="s">
         <v>38</v>
       </c>
@@ -8357,7 +8423,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="20" t="s">
         <v>38</v>
       </c>
@@ -8368,7 +8434,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="20" t="s">
         <v>38</v>
       </c>
@@ -8379,7 +8445,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="20" t="s">
         <v>38</v>
       </c>
@@ -8390,7 +8456,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="20" t="s">
         <v>38</v>
       </c>
@@ -8401,7 +8467,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
         <v>38</v>
       </c>
@@ -8412,7 +8478,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="20" t="s">
         <v>38</v>
       </c>
@@ -8423,7 +8489,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="20" t="s">
         <v>38</v>
       </c>
@@ -8434,7 +8500,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="20" t="s">
         <v>38</v>
       </c>
@@ -8445,7 +8511,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="20" t="s">
         <v>38</v>
       </c>
@@ -8456,7 +8522,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="20" t="s">
         <v>38</v>
       </c>
@@ -8467,9 +8533,9 @@
         <v>494</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B32" s="30" t="s">
         <v>495</v>
@@ -8478,9 +8544,9 @@
         <v>496</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B33" s="26" t="s">
         <v>497</v>
@@ -8489,9 +8555,9 @@
         <v>465</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B34" s="21" t="s">
         <v>498</v>
@@ -8500,9 +8566,9 @@
         <v>496</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B35" s="30" t="s">
         <v>499</v>
@@ -8511,9 +8577,9 @@
         <v>500</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B36" s="30" t="s">
         <v>501</v>
@@ -8522,9 +8588,9 @@
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B37" s="26" t="s">
         <v>502</v>
@@ -8533,9 +8599,9 @@
         <v>503</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="60" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B38" s="21" t="s">
         <v>504</v>
@@ -8544,9 +8610,9 @@
         <v>505</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="60" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B39" s="30" t="s">
         <v>506</v>
@@ -8555,9 +8621,9 @@
         <v>447</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="60" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B40" s="26" t="s">
         <v>507</v>
@@ -8566,9 +8632,9 @@
         <v>470</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="60" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B41" s="21" t="s">
         <v>508</v>
@@ -8577,9 +8643,9 @@
         <v>489</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="60" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B42" s="30" t="s">
         <v>509</v>
@@ -8588,9 +8654,9 @@
         <v>510</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="60" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B43" s="30" t="s">
         <v>511</v>
@@ -8599,9 +8665,9 @@
         <v>512</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="60" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B44" s="26" t="s">
         <v>513</v>
@@ -8610,9 +8676,9 @@
         <v>514</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="60" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B45" s="72" t="s">
         <v>493</v>
@@ -8621,9 +8687,9 @@
         <v>465</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="62" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B46" s="63" t="s">
         <v>515</v>
@@ -8632,9 +8698,9 @@
         <v>516</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="62" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B47" s="63" t="s">
         <v>517</v>
@@ -8643,9 +8709,9 @@
         <v>518</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="62" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B48" s="44" t="s">
         <v>519</v>
@@ -8654,9 +8720,9 @@
         <v>520</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="62" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B49" s="74" t="s">
         <v>521</v>
@@ -8665,9 +8731,9 @@
         <v>522</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="62" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B50" s="21" t="s">
         <v>523</v>
@@ -8676,9 +8742,9 @@
         <v>518</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="62" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B51" s="30" t="s">
         <v>524</v>
@@ -8687,9 +8753,9 @@
         <v>514</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="62" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B52" s="31" t="s">
         <v>525</v>
@@ -8698,9 +8764,9 @@
         <v>526</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="62" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B53" s="21" t="s">
         <v>527</v>
@@ -8709,9 +8775,9 @@
         <v>528</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="62" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B54" s="26" t="s">
         <v>529</v>
@@ -8720,9 +8786,9 @@
         <v>528</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>530</v>
@@ -8731,9 +8797,9 @@
         <v>531</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="62" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B56" s="64" t="s">
         <v>532</v>
@@ -8742,9 +8808,9 @@
         <v>533</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B57" s="30" t="s">
         <v>534</v>
@@ -8753,9 +8819,9 @@
         <v>535</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="60" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B58" s="30" t="s">
         <v>536</v>
@@ -8764,9 +8830,9 @@
         <v>447</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B59" s="26" t="s">
         <v>537</v>
@@ -8775,9 +8841,9 @@
         <v>538</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="60" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B60" s="21" t="s">
         <v>539</v>
@@ -8786,7 +8852,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="20" t="s">
         <v>73</v>
       </c>
@@ -8797,7 +8863,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="60" t="s">
         <v>73</v>
       </c>
@@ -8808,7 +8874,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="20" t="s">
         <v>73</v>
       </c>
@@ -8819,7 +8885,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="60" t="s">
         <v>73</v>
       </c>
@@ -8830,7 +8896,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="20" t="s">
         <v>73</v>
       </c>
@@ -8841,7 +8907,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="60" t="s">
         <v>73</v>
       </c>
@@ -8852,7 +8918,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="20" t="s">
         <v>73</v>
       </c>
@@ -8863,7 +8929,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="5" t="s">
         <v>73</v>
       </c>
@@ -8874,7 +8940,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="59" t="s">
         <v>73</v>
       </c>
@@ -8885,7 +8951,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="5" t="s">
         <v>73</v>
       </c>
@@ -8896,7 +8962,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="59" t="s">
         <v>73</v>
       </c>
@@ -8907,7 +8973,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="5" t="s">
         <v>73</v>
       </c>
@@ -8918,7 +8984,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="59" t="s">
         <v>73</v>
       </c>
@@ -8929,7 +8995,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="5" t="s">
         <v>73</v>
       </c>
@@ -8940,7 +9006,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="59" t="s">
         <v>73</v>
       </c>
@@ -8951,7 +9017,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="5" t="s">
         <v>73</v>
       </c>
@@ -8962,7 +9028,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="59" t="s">
         <v>73</v>
       </c>
@@ -8973,7 +9039,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="5" t="s">
         <v>73</v>
       </c>
@@ -8984,7 +9050,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="59" t="s">
         <v>73</v>
       </c>
@@ -8995,7 +9061,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
         <v>73</v>
       </c>
@@ -9006,7 +9072,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="20" t="s">
         <v>73</v>
       </c>
@@ -9017,7 +9083,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="20" t="s">
         <v>73</v>
       </c>
@@ -9028,7 +9094,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="20" t="s">
         <v>73</v>
       </c>
@@ -9039,7 +9105,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="20" t="s">
         <v>73</v>
       </c>
@@ -9050,7 +9116,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="20" t="s">
         <v>73</v>
       </c>
@@ -9061,9 +9127,9 @@
         <v>516</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B86" s="49" t="s">
         <v>557</v>
@@ -9072,9 +9138,9 @@
         <v>558</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="17" x14ac:dyDescent="0.4">
       <c r="A87" s="53" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B87" s="47" t="s">
         <v>559</v>
@@ -9083,9 +9149,9 @@
         <v>560</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="17" x14ac:dyDescent="0.4">
       <c r="A88" s="53" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B88" s="68" t="s">
         <v>8</v>
@@ -9094,9 +9160,9 @@
         <v>561</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="17" x14ac:dyDescent="0.4">
       <c r="A89" s="53" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B89" s="49" t="s">
         <v>451</v>
@@ -9105,9 +9171,9 @@
         <v>562</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="17" x14ac:dyDescent="0.4">
       <c r="A90" s="53" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B90" s="47" t="s">
         <v>563</v>
@@ -9116,9 +9182,9 @@
         <v>564</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="17" x14ac:dyDescent="0.4">
       <c r="A91" s="53" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B91" s="66" t="s">
         <v>565</v>
@@ -9127,9 +9193,9 @@
         <v>470</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A92" s="61" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B92" s="34" t="s">
         <v>566</v>
@@ -9138,9 +9204,9 @@
         <v>470</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="32.25" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A93" s="61" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B93" s="69" t="s">
         <v>567</v>
@@ -9149,9 +9215,9 @@
         <v>568</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A94" s="61" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B94" s="69" t="s">
         <v>569</v>
@@ -9160,9 +9226,9 @@
         <v>489</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A95" s="61" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B95" s="33" t="s">
         <v>570</v>
@@ -9171,9 +9237,9 @@
         <v>571</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A96" s="61" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B96" s="67" t="s">
         <v>572</v>
@@ -9182,9 +9248,9 @@
         <v>573</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A97" s="61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B97" s="35" t="s">
         <v>574</v>
@@ -9193,9 +9259,9 @@
         <v>575</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A98" s="61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B98" s="33" t="s">
         <v>576</v>
@@ -9204,9 +9270,9 @@
         <v>577</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A99" s="61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B99" s="71" t="s">
         <v>578</v>
@@ -9215,9 +9281,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A100" s="61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B100" s="34" t="s">
         <v>580</v>
@@ -9226,9 +9292,9 @@
         <v>452</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="32.25" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" ht="31.5" x14ac:dyDescent="0.4">
       <c r="A101" s="61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B101" s="35" t="s">
         <v>581</v>
@@ -9237,9 +9303,9 @@
         <v>514</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A102" s="61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B102" s="33" t="s">
         <v>582</v>
@@ -9248,9 +9314,9 @@
         <v>496</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A103" s="61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B103" s="34" t="s">
         <v>583</v>
@@ -9259,9 +9325,9 @@
         <v>584</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A104" s="61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B104" s="34" t="s">
         <v>585</v>
@@ -9270,9 +9336,9 @@
         <v>586</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A105" s="61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B105" s="35" t="s">
         <v>587</v>
@@ -9281,9 +9347,9 @@
         <v>546</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A106" s="61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B106" s="33" t="s">
         <v>588</v>
@@ -9292,9 +9358,9 @@
         <v>589</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A107" s="61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B107" s="34" t="s">
         <v>590</v>
@@ -9303,9 +9369,9 @@
         <v>591</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A108" s="61" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B108" s="35" t="s">
         <v>592</v>
@@ -9314,9 +9380,9 @@
         <v>593</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B109" t="s">
         <v>594</v>
@@ -9325,9 +9391,9 @@
         <v>595</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B110" t="s">
         <v>596</v>
@@ -9336,9 +9402,9 @@
         <v>489</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B111" t="s">
         <v>597</v>
@@ -9347,9 +9413,9 @@
         <v>510</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B112" t="s">
         <v>598</v>
@@ -9358,9 +9424,9 @@
         <v>470</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B113" t="s">
         <v>599</v>
@@ -9369,9 +9435,9 @@
         <v>584</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B114" t="s">
         <v>600</v>
@@ -9380,9 +9446,9 @@
         <v>487</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B115" t="s">
         <v>601</v>
@@ -9391,9 +9457,9 @@
         <v>518</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B116" t="s">
         <v>602</v>
@@ -9402,9 +9468,9 @@
         <v>562</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B117" t="s">
         <v>602</v>
@@ -9413,9 +9479,9 @@
         <v>603</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B118" t="s">
         <v>604</v>
@@ -9424,9 +9490,9 @@
         <v>605</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B119" t="s">
         <v>606</v>
@@ -9435,7 +9501,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>263</v>
       </c>
@@ -9446,7 +9512,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>263</v>
       </c>
@@ -9457,7 +9523,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>263</v>
       </c>
@@ -9468,7 +9534,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>263</v>
       </c>
@@ -9479,7 +9545,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>263</v>
       </c>
@@ -9490,7 +9556,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>263</v>
       </c>
@@ -9501,7 +9567,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>263</v>
       </c>
@@ -9512,7 +9578,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>263</v>
       </c>
@@ -9523,7 +9589,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>263</v>
       </c>
@@ -9534,7 +9600,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>263</v>
       </c>
@@ -9545,7 +9611,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>263</v>
       </c>
@@ -9556,7 +9622,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>263</v>
       </c>
@@ -9567,7 +9633,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>263</v>
       </c>
@@ -9578,7 +9644,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>350</v>
       </c>
@@ -9589,7 +9655,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>350</v>
       </c>
@@ -9600,7 +9666,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>350</v>
       </c>
@@ -9611,7 +9677,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>350</v>
       </c>
@@ -9622,7 +9688,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>350</v>
       </c>
@@ -9633,7 +9699,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>350</v>
       </c>
@@ -9644,7 +9710,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>350</v>
       </c>
@@ -9655,7 +9721,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>350</v>
       </c>
@@ -9666,7 +9732,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>350</v>
       </c>
@@ -9677,7 +9743,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>350</v>
       </c>
@@ -9688,7 +9754,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>350</v>
       </c>
@@ -9699,7 +9765,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>193</v>
       </c>
@@ -9710,7 +9776,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>193</v>
       </c>
@@ -9721,7 +9787,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>193</v>
       </c>
@@ -9732,7 +9798,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>193</v>
       </c>
@@ -9743,7 +9809,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>193</v>
       </c>
@@ -9754,7 +9820,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>193</v>
       </c>
@@ -9765,7 +9831,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>193</v>
       </c>
@@ -9776,7 +9842,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>193</v>
       </c>
@@ -9787,7 +9853,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>193</v>
       </c>
@@ -9798,7 +9864,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>193</v>
       </c>
@@ -9809,7 +9875,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>193</v>
       </c>
@@ -9820,7 +9886,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>193</v>
       </c>
@@ -9831,7 +9897,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>193</v>
       </c>
@@ -9842,7 +9908,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>193</v>
       </c>
@@ -9853,7 +9919,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>193</v>
       </c>
@@ -9864,7 +9930,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>193</v>
       </c>
@@ -9875,7 +9941,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>193</v>
       </c>
@@ -9886,7 +9952,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>193</v>
       </c>
@@ -9897,7 +9963,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>312</v>
       </c>
@@ -9908,7 +9974,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>312</v>
       </c>
@@ -9919,7 +9985,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>312</v>
       </c>
@@ -9930,7 +9996,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>312</v>
       </c>
@@ -9941,7 +10007,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>312</v>
       </c>
@@ -9952,7 +10018,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>312</v>
       </c>
@@ -9963,7 +10029,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>312</v>
       </c>
@@ -9974,7 +10040,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>312</v>
       </c>
@@ -9985,7 +10051,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>312</v>
       </c>
@@ -9996,7 +10062,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>312</v>
       </c>
@@ -10007,7 +10073,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>312</v>
       </c>
@@ -10018,7 +10084,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>312</v>
       </c>
@@ -10029,7 +10095,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>312</v>
       </c>
@@ -10040,7 +10106,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>312</v>
       </c>
@@ -10051,7 +10117,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>312</v>
       </c>
@@ -10062,7 +10128,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>312</v>
       </c>
@@ -10073,7 +10139,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>312</v>
       </c>
@@ -10084,7 +10150,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>312</v>
       </c>
@@ -10095,7 +10161,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>312</v>
       </c>
@@ -10106,7 +10172,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>312</v>
       </c>
@@ -10117,7 +10183,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>312</v>
       </c>
@@ -10128,7 +10194,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>312</v>
       </c>
@@ -10139,7 +10205,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>312</v>
       </c>
@@ -10150,7 +10216,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>312</v>
       </c>
@@ -10161,7 +10227,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>312</v>
       </c>
@@ -10172,7 +10238,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>312</v>
       </c>
@@ -10183,7 +10249,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>312</v>
       </c>
@@ -10194,7 +10260,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>312</v>
       </c>
@@ -10205,7 +10271,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>312</v>
       </c>
@@ -10216,7 +10282,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>312</v>
       </c>
@@ -10227,7 +10293,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>312</v>
       </c>
@@ -10238,7 +10304,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>312</v>
       </c>
@@ -10249,7 +10315,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>312</v>
       </c>
@@ -10260,7 +10326,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>312</v>
       </c>
@@ -10271,7 +10337,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>337</v>
       </c>
@@ -10282,7 +10348,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>337</v>
       </c>
@@ -10293,7 +10359,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>337</v>
       </c>
@@ -10304,7 +10370,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>337</v>
       </c>
@@ -10315,7 +10381,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>337</v>
       </c>
@@ -10326,7 +10392,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>337</v>
       </c>
@@ -10337,7 +10403,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>337</v>
       </c>
@@ -10348,7 +10414,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>337</v>
       </c>
@@ -10359,7 +10425,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>337</v>
       </c>
@@ -10370,7 +10436,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>337</v>
       </c>
@@ -10381,7 +10447,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>337</v>
       </c>
@@ -10392,7 +10458,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>337</v>
       </c>
@@ -10403,7 +10469,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>337</v>
       </c>
@@ -10414,7 +10480,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>337</v>
       </c>
@@ -10425,7 +10491,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>337</v>
       </c>
@@ -10436,7 +10502,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>337</v>
       </c>
@@ -10447,7 +10513,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>337</v>
       </c>
@@ -10458,7 +10524,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>337</v>
       </c>
@@ -10469,7 +10535,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>337</v>
       </c>
@@ -10480,7 +10546,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>337</v>
       </c>
@@ -10491,7 +10557,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>337</v>
       </c>
@@ -10502,7 +10568,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>337</v>
       </c>
@@ -10513,7 +10579,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>337</v>
       </c>
@@ -10521,120 +10587,120 @@
         <v>710</v>
       </c>
       <c r="C218" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>337</v>
       </c>
       <c r="B219" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C219" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>337</v>
       </c>
       <c r="B220" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C220" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>337</v>
       </c>
       <c r="B221" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C221" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>337</v>
       </c>
       <c r="B222" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C222" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>337</v>
       </c>
       <c r="B223" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C223" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>337</v>
       </c>
       <c r="B224" t="s">
+        <v>719</v>
+      </c>
+      <c r="C224" t="s">
         <v>718</v>
       </c>
-      <c r="C224" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>337</v>
       </c>
       <c r="B225" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C225" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>337</v>
       </c>
       <c r="B226" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C226" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>337</v>
       </c>
       <c r="B227" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C227" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>337</v>
       </c>
       <c r="B228" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C228" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>337</v>
       </c>
@@ -10642,21 +10708,21 @@
         <v>529</v>
       </c>
       <c r="C229" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>337</v>
       </c>
       <c r="B230" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C230" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>290</v>
       </c>
@@ -10667,7 +10733,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>290</v>
       </c>
@@ -10678,7 +10744,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>290</v>
       </c>
@@ -10689,7 +10755,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>290</v>
       </c>
@@ -10700,7 +10766,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>290</v>
       </c>
@@ -10711,7 +10777,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>290</v>
       </c>
@@ -10722,7 +10788,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>290</v>
       </c>
@@ -10733,7 +10799,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>290</v>
       </c>
@@ -10744,7 +10810,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>290</v>
       </c>
@@ -10755,7 +10821,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>290</v>
       </c>
@@ -10766,7 +10832,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>290</v>
       </c>
@@ -10777,7 +10843,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>290</v>
       </c>
@@ -10788,7 +10854,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>290</v>
       </c>
@@ -10799,7 +10865,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>290</v>
       </c>
@@ -10810,7 +10876,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>290</v>
       </c>
@@ -10821,7 +10887,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>290</v>
       </c>
@@ -10832,7 +10898,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>290</v>
       </c>
@@ -10843,84 +10909,84 @@
         <v>662</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>290</v>
       </c>
       <c r="B248" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C248" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>290</v>
       </c>
       <c r="B249" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C249" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>290</v>
       </c>
       <c r="B250" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C250" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>290</v>
       </c>
       <c r="B251" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C251" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>290</v>
       </c>
       <c r="B252" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C252" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>290</v>
       </c>
       <c r="B253" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C253" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>290</v>
       </c>
       <c r="B254" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C254" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>290</v>
       </c>
@@ -10931,106 +10997,106 @@
         <v>544</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>290</v>
       </c>
       <c r="B256" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C256" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>290</v>
       </c>
       <c r="B257" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C257" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>290</v>
       </c>
       <c r="B258" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C258" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>290</v>
       </c>
       <c r="B259" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C259" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>290</v>
       </c>
       <c r="B260" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C260" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>290</v>
       </c>
       <c r="B261" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C261" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>290</v>
       </c>
       <c r="B262" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C262" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>290</v>
       </c>
       <c r="B263" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C263" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>290</v>
       </c>
       <c r="B264" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C264" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>376</v>
       </c>
@@ -11038,10 +11104,10 @@
         <v>442</v>
       </c>
       <c r="C265" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>376</v>
       </c>
@@ -11049,65 +11115,65 @@
         <v>444</v>
       </c>
       <c r="C266" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>376</v>
       </c>
       <c r="B267" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C267" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>376</v>
       </c>
       <c r="B268" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C268" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>376</v>
       </c>
       <c r="B269" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C269" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>376</v>
       </c>
       <c r="B270" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C270" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>376</v>
       </c>
       <c r="B271" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C271" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>376</v>
       </c>
@@ -11118,29 +11184,29 @@
         <v>591</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>376</v>
       </c>
       <c r="B273" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C273" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>376</v>
       </c>
       <c r="B274" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C274" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>402</v>
       </c>
@@ -11148,10 +11214,10 @@
         <v>442</v>
       </c>
       <c r="C275" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>402</v>
       </c>
@@ -11159,65 +11225,65 @@
         <v>444</v>
       </c>
       <c r="C276" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>402</v>
       </c>
       <c r="B277" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C277" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>402</v>
       </c>
       <c r="B278" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C278" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>402</v>
       </c>
       <c r="B279" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C279" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>402</v>
       </c>
       <c r="B280" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C280" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>402</v>
       </c>
       <c r="B281" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C281" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>402</v>
       </c>
@@ -11228,84 +11294,84 @@
         <v>571</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>402</v>
       </c>
       <c r="B283" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C283" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>402</v>
       </c>
       <c r="B284" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C284" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>423</v>
       </c>
       <c r="B285" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C285" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>423</v>
       </c>
       <c r="B286" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C286" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>423</v>
       </c>
       <c r="B287" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C287" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>423</v>
       </c>
       <c r="B288" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C288" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>423</v>
       </c>
       <c r="B289" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C289" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>423</v>
       </c>
@@ -11313,98 +11379,98 @@
         <v>3</v>
       </c>
       <c r="C290" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>423</v>
       </c>
       <c r="B291" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C291" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>423</v>
       </c>
       <c r="B292" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C292" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>423</v>
       </c>
       <c r="B293" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C293" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>423</v>
       </c>
       <c r="B294" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C294" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>423</v>
       </c>
       <c r="B295" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C295" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>423</v>
       </c>
       <c r="B296" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C296" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>423</v>
       </c>
       <c r="B297" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C297" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>423</v>
       </c>
       <c r="B298" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C298" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>423</v>
       </c>
@@ -11415,51 +11481,51 @@
         <v>483</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>423</v>
       </c>
       <c r="B300" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C300" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>423</v>
       </c>
       <c r="B301" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C301" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>423</v>
       </c>
       <c r="B302" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C302" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>423</v>
       </c>
       <c r="B303" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C303" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>423</v>
       </c>
@@ -11470,30 +11536,30 @@
         <v>481</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>423</v>
       </c>
       <c r="B305" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C305" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>423</v>
       </c>
       <c r="B306" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C306" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C306" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <autoFilter ref="A1:C108" xr:uid="{00000000-0001-0000-0300-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C108">
       <sortCondition ref="A1:A108"/>
     </sortState>
